--- a/도면검토리포트_최종.xlsx
+++ b/도면검토리포트_최종.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K537"/>
+  <dimension ref="A1:K538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22148,1815 +22148,1780 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="inlineStr">
+      <c r="A412" t="inlineStr">
         <is>
           <t>BA - 101</t>
         </is>
       </c>
-      <c r="B412" s="1" t="inlineStr"/>
-      <c r="C412" s="1" t="inlineStr">
+      <c r="C412" t="inlineStr">
         <is>
           <t>영구저류조(SL+53 ) / 지하 PIT층(SL+56.255) 평면도</t>
         </is>
       </c>
-      <c r="D412" s="1" t="inlineStr">
+      <c r="D412" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E412" s="1" t="inlineStr">
+      <c r="E412" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F412" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G412" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H412" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I412" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J412" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K412" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>BA - 101</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>영구저류조(SL+53.355) / 지하 PIT층(SL+56.255) 평면도</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="inlineStr">
+      <c r="A413" t="inlineStr">
         <is>
           <t>BA - 102</t>
         </is>
       </c>
-      <c r="B413" s="1" t="inlineStr"/>
-      <c r="C413" s="1" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>영구저류조(SL+53 ) / 지하 PIT층(SL+56.255) 확대평면도</t>
         </is>
       </c>
-      <c r="D413" s="1" t="inlineStr">
+      <c r="D413" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E413" s="1" t="inlineStr">
+      <c r="E413" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F413" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G413" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H413" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I413" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J413" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K413" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>BA - 102</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>영구저류조(SL+53.355) / 지하 PIT층(SL+56.255) 확대평면도</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="inlineStr">
+      <c r="A414" t="inlineStr">
         <is>
           <t>BA - 103</t>
         </is>
       </c>
-      <c r="B414" s="1" t="inlineStr"/>
-      <c r="C414" s="1" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>지하3층(SL+61 /SL+59 )주차장 평면도</t>
         </is>
       </c>
-      <c r="D414" s="1" t="inlineStr">
+      <c r="D414" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E414" s="1" t="inlineStr">
+      <c r="E414" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F414" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G414" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H414" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I414" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J414" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K414" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>BA - 103</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>지하3층(SL+61.30/SL+59.30) 주차장 평면도</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="inlineStr">
+      <c r="A415" t="inlineStr">
         <is>
           <t>BA - 104</t>
         </is>
       </c>
-      <c r="B415" s="1" t="inlineStr"/>
-      <c r="C415" s="1" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>지하3층(SL+61 /SL+59 )주차장 확대평면도-1</t>
         </is>
       </c>
-      <c r="D415" s="1" t="inlineStr">
+      <c r="D415" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E415" s="1" t="inlineStr">
+      <c r="E415" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F415" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G415" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H415" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I415" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J415" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K415" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>BA - 104</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>지하3층(SL+61.30/SL+59.30) 주차장 확대평면도-1</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="inlineStr">
+      <c r="A416" t="inlineStr">
         <is>
           <t>BA - 105</t>
         </is>
       </c>
-      <c r="B416" s="1" t="inlineStr"/>
-      <c r="C416" s="1" t="inlineStr">
+      <c r="C416" t="inlineStr">
         <is>
           <t>지하3층(SL+61 /SL+59 )주차장 확대평면도-2</t>
         </is>
       </c>
-      <c r="D416" s="1" t="inlineStr">
+      <c r="D416" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E416" s="1" t="inlineStr">
+      <c r="E416" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F416" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G416" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H416" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I416" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J416" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K416" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>BA - 105</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>지하3층(SL+61.30/SL+59.30) 주차장 확대평면도-2</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="inlineStr">
+      <c r="A417" t="inlineStr">
         <is>
           <t>BA - 106</t>
         </is>
       </c>
-      <c r="B417" s="1" t="inlineStr"/>
-      <c r="C417" s="1" t="inlineStr">
+      <c r="C417" t="inlineStr">
         <is>
           <t>지하3층(SL+61 /SL+59 )주차장 확대평면도-3</t>
         </is>
       </c>
-      <c r="D417" s="1" t="inlineStr">
+      <c r="D417" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E417" s="1" t="inlineStr">
+      <c r="E417" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F417" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G417" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H417" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I417" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J417" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K417" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>BA - 106</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>지하3층(SL+61.30/SL+59.30) 주차장 확대평면도-3</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="inlineStr">
+      <c r="A418" t="inlineStr">
         <is>
           <t>BA - 107</t>
         </is>
       </c>
-      <c r="B418" s="1" t="inlineStr"/>
-      <c r="C418" s="1" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>지하2층(SL+64 /SL+67.00)주차장 평면도</t>
         </is>
       </c>
-      <c r="D418" s="1" t="inlineStr">
+      <c r="D418" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E418" s="1" t="inlineStr">
+      <c r="E418" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F418" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G418" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H418" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I418" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J418" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K418" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>BA - 107</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>지하2층(SL+64.80/SL+67.00) 주차장 평면도</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="inlineStr">
+      <c r="A419" t="inlineStr">
         <is>
           <t>BA - 108</t>
         </is>
       </c>
-      <c r="B419" s="1" t="inlineStr"/>
-      <c r="C419" s="1" t="inlineStr">
+      <c r="C419" t="inlineStr">
         <is>
           <t>지하2층(SL+64 /SL+67.00)주차장 확대평면도-1</t>
         </is>
       </c>
-      <c r="D419" s="1" t="inlineStr">
+      <c r="D419" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E419" s="1" t="inlineStr">
+      <c r="E419" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F419" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G419" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H419" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I419" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J419" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K419" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>BA - 108</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>지하2층(SL+64.80/SL+67.00) 주차장 확대평면도-1</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>BA - 109</t>
         </is>
       </c>
-      <c r="B420" s="1" t="inlineStr"/>
-      <c r="C420" s="1" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>지하2층(SL+64 /SL+67.00)주차장 확대평면도-2</t>
         </is>
       </c>
-      <c r="D420" s="1" t="inlineStr">
+      <c r="D420" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E420" s="1" t="inlineStr">
+      <c r="E420" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F420" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G420" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H420" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I420" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J420" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K420" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>BA - 109</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>지하2층(SL+64.80/SL+67.00) 주차장 확대평면도-2</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="inlineStr">
+      <c r="A421" t="inlineStr">
         <is>
           <t>BA - 110</t>
         </is>
       </c>
-      <c r="B421" s="1" t="inlineStr"/>
-      <c r="C421" s="1" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>지하2층(SL+64 /SL+67.00)주차장 확대평면도-3</t>
         </is>
       </c>
-      <c r="D421" s="1" t="inlineStr">
+      <c r="D421" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E421" s="1" t="inlineStr">
+      <c r="E421" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F421" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G421" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H421" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I421" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J421" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K421" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>BA - 110</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>지하2층(SL+64.80/SL+67.00) 주차장 확대평면도-3</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="inlineStr">
+      <c r="A422" t="inlineStr">
         <is>
           <t>BA - 111</t>
         </is>
       </c>
-      <c r="B422" s="1" t="inlineStr"/>
-      <c r="C422" s="1" t="inlineStr">
+      <c r="C422" t="inlineStr">
         <is>
           <t>지하2층(SL+64 /SL+67.00)주차장 확대평면도-4</t>
         </is>
       </c>
-      <c r="D422" s="1" t="inlineStr">
+      <c r="D422" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E422" s="1" t="inlineStr">
+      <c r="E422" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F422" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G422" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H422" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I422" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J422" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K422" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>BA - 111</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>지하2층(SL+64.80/SL+67.00) 주차장 확대평면도-4</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="inlineStr">
+      <c r="A423" t="inlineStr">
         <is>
           <t>BA - 112</t>
         </is>
       </c>
-      <c r="B423" s="1" t="inlineStr"/>
-      <c r="C423" s="1" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>지하1층(SL+70 )주차장 평면도</t>
         </is>
       </c>
-      <c r="D423" s="1" t="inlineStr">
+      <c r="D423" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E423" s="1" t="inlineStr">
+      <c r="E423" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F423" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G423" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H423" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I423" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J423" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K423" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>BA - 112</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>지하1층(SL+70.50) 주차장 평면도</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="inlineStr">
+      <c r="A424" t="inlineStr">
         <is>
           <t>BA - 113</t>
         </is>
       </c>
-      <c r="B424" s="1" t="inlineStr"/>
-      <c r="C424" s="1" t="inlineStr">
+      <c r="C424" t="inlineStr">
         <is>
           <t>지하1층(SL+70 )주차장 확대평면도-1</t>
         </is>
       </c>
-      <c r="D424" s="1" t="inlineStr">
+      <c r="D424" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E424" s="1" t="inlineStr">
+      <c r="E424" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F424" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G424" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H424" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I424" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J424" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K424" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>BA - 113</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>지하1층(SL+70.50) 주차장 확대평면도-1</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="inlineStr">
+      <c r="A425" t="inlineStr">
         <is>
           <t>BA - 114</t>
         </is>
       </c>
-      <c r="B425" s="1" t="inlineStr"/>
-      <c r="C425" s="1" t="inlineStr">
+      <c r="C425" t="inlineStr">
         <is>
           <t>지하1층(SL+70 )주차장 확대평면도-2</t>
         </is>
       </c>
-      <c r="D425" s="1" t="inlineStr">
+      <c r="D425" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E425" s="1" t="inlineStr">
+      <c r="E425" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F425" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G425" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H425" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I425" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J425" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K425" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>BA - 114</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>지하1층(SL+70.50) 주차장 확대평면도-2</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="inlineStr">
+      <c r="A426" t="inlineStr">
         <is>
           <t>BA - 115</t>
         </is>
       </c>
-      <c r="B426" s="1" t="inlineStr"/>
-      <c r="C426" s="1" t="inlineStr">
+      <c r="C426" t="inlineStr">
         <is>
           <t>지하1층(SL+70 )주차장 확대평면도-3</t>
         </is>
       </c>
-      <c r="D426" s="1" t="inlineStr">
+      <c r="D426" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="E426" s="1" t="inlineStr">
+      <c r="E426" t="inlineStr">
         <is>
           <t>1/400</t>
         </is>
       </c>
-      <c r="F426" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G426" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H426" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I426" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J426" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K426" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>BA - 115</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>지하1층(SL+70.50) 주차장 확대평면도-3</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>1/400</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>BA-101_1BL 지하주차장 평면도.dwg</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="inlineStr">
+      <c r="A427" t="inlineStr">
         <is>
           <t>BA - 116</t>
         </is>
       </c>
-      <c r="B427" s="1" t="inlineStr"/>
-      <c r="C427" s="1" t="inlineStr">
+      <c r="C427" t="inlineStr">
         <is>
           <t>지하주차장 종 단면도</t>
         </is>
       </c>
-      <c r="D427" s="1" t="inlineStr">
+      <c r="D427" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E427" s="1" t="inlineStr">
+      <c r="E427" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F427" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G427" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H427" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I427" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J427" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K427" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>BA - 116</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>지하주차장 종-1,종-2 단면도</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>BA-116_1BL 지하주차장 단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="inlineStr">
+      <c r="A428" t="inlineStr">
         <is>
           <t>BA - 117</t>
         </is>
       </c>
-      <c r="B428" s="1" t="inlineStr"/>
-      <c r="C428" s="1" t="inlineStr">
+      <c r="C428" t="inlineStr">
         <is>
           <t>지하주차장 , 횡-2 단면도</t>
         </is>
       </c>
-      <c r="D428" s="1" t="inlineStr">
+      <c r="D428" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E428" s="1" t="inlineStr">
+      <c r="E428" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F428" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G428" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H428" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I428" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J428" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K428" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>BA - 117</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>지하주차장 횡-1,횡-2 단면도</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>BA-116_1BL 지하주차장 단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="inlineStr">
+      <c r="A429" t="inlineStr">
         <is>
           <t>BA - 121</t>
         </is>
       </c>
-      <c r="B429" s="1" t="inlineStr"/>
-      <c r="C429" s="1" t="inlineStr">
+      <c r="C429" t="inlineStr">
         <is>
           <t>지하주차장 경사로#1 평면도</t>
         </is>
       </c>
-      <c r="D429" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E429" s="1" t="inlineStr">
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F429" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G429" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H429" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I429" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J429" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K429" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>BA - 121</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#1 평면도</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="inlineStr">
+      <c r="A430" t="inlineStr">
         <is>
           <t>BA - 122</t>
         </is>
       </c>
-      <c r="B430" s="1" t="inlineStr"/>
-      <c r="C430" s="1" t="inlineStr">
+      <c r="C430" t="inlineStr">
         <is>
           <t>경사로#1 단면도</t>
         </is>
       </c>
-      <c r="D430" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E430" s="1" t="inlineStr">
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F430" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G430" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H430" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I430" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J430" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K430" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>BA - 122</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#1 단면도</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="inlineStr">
+      <c r="A431" t="inlineStr">
         <is>
           <t>BA - 123</t>
         </is>
       </c>
-      <c r="B431" s="1" t="inlineStr"/>
-      <c r="C431" s="1" t="inlineStr">
+      <c r="C431" t="inlineStr">
         <is>
           <t>경사로#2 평면도</t>
         </is>
       </c>
-      <c r="D431" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E431" s="1" t="inlineStr">
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F431" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G431" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H431" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I431" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J431" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K431" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>BA - 123</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#2 평면도</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="inlineStr">
+      <c r="A432" t="inlineStr">
         <is>
           <t>BA - 124</t>
         </is>
       </c>
-      <c r="B432" s="1" t="inlineStr"/>
-      <c r="C432" s="1" t="inlineStr">
+      <c r="C432" t="inlineStr">
         <is>
           <t>경사로#2 단면도</t>
         </is>
       </c>
-      <c r="D432" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E432" s="1" t="inlineStr">
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F432" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G432" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H432" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I432" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J432" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K432" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>BA - 124</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#2 단면도</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="inlineStr">
+      <c r="A433" t="inlineStr">
         <is>
           <t>BA - 125</t>
         </is>
       </c>
-      <c r="B433" s="1" t="inlineStr"/>
-      <c r="C433" s="1" t="inlineStr">
+      <c r="C433" t="inlineStr">
         <is>
           <t>경사로#3 평면도</t>
         </is>
       </c>
-      <c r="D433" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E433" s="1" t="inlineStr">
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F433" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G433" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H433" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I433" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J433" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K433" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>BA - 125</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#3 평면도</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="inlineStr">
+      <c r="A434" t="inlineStr">
         <is>
           <t>BA - 126</t>
         </is>
       </c>
-      <c r="B434" s="1" t="inlineStr"/>
-      <c r="C434" s="1" t="inlineStr">
+      <c r="C434" t="inlineStr">
         <is>
           <t>경사로#3 단면도</t>
         </is>
       </c>
-      <c r="D434" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E434" s="1" t="inlineStr">
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F434" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G434" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H434" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I434" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J434" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K434" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>BA - 126</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#3 단면도</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="inlineStr">
+      <c r="A435" t="inlineStr">
         <is>
           <t>BA - 127</t>
         </is>
       </c>
-      <c r="B435" s="1" t="inlineStr"/>
-      <c r="C435" s="1" t="inlineStr">
+      <c r="C435" t="inlineStr">
         <is>
           <t>경사로#4 평면도, 단면도</t>
         </is>
       </c>
-      <c r="D435" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E435" s="1" t="inlineStr">
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F435" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G435" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H435" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I435" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J435" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K435" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>BA - 127</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#4 평면,단면도</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="inlineStr">
+      <c r="A436" t="inlineStr">
         <is>
           <t>BA - 128</t>
         </is>
       </c>
-      <c r="B436" s="1" t="inlineStr"/>
-      <c r="C436" s="1" t="inlineStr">
+      <c r="C436" t="inlineStr">
         <is>
           <t>경사로#5 평면도, 단면도</t>
         </is>
       </c>
-      <c r="D436" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E436" s="1" t="inlineStr">
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F436" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G436" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H436" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I436" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J436" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K436" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>BA - 128</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#5 평면,단면도</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="inlineStr">
+      <c r="A437" t="inlineStr">
         <is>
           <t>BA - 129</t>
         </is>
       </c>
-      <c r="B437" s="1" t="inlineStr"/>
-      <c r="C437" s="1" t="inlineStr">
+      <c r="C437" t="inlineStr">
         <is>
           <t>경사로#5 단면도</t>
         </is>
       </c>
-      <c r="D437" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E437" s="1" t="inlineStr">
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F437" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G437" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H437" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I437" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J437" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K437" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>BA - 129</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#5 단면도</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="inlineStr">
+      <c r="A438" t="inlineStr">
         <is>
           <t>BA - 130</t>
         </is>
       </c>
-      <c r="B438" s="1" t="inlineStr"/>
-      <c r="C438" s="1" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>경사로#6 평면,단면도</t>
         </is>
       </c>
-      <c r="D438" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E438" s="1" t="inlineStr">
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F438" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G438" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H438" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I438" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J438" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K438" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>BA - 130</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#6 평면,단면도</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="inlineStr">
+      <c r="A439" t="inlineStr">
         <is>
           <t>BA - 131</t>
         </is>
       </c>
-      <c r="B439" s="1" t="inlineStr"/>
-      <c r="C439" s="1" t="inlineStr">
+      <c r="C439" t="inlineStr">
         <is>
           <t>경사로#7 평면,단면도</t>
         </is>
       </c>
-      <c r="D439" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E439" s="1" t="inlineStr">
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F439" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G439" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H439" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I439" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J439" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K439" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>BA - 131</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>지하주차장 경사로#7 평면,단면도</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>BA-121_1BL 경사로 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="inlineStr">
+      <c r="A440" t="inlineStr">
         <is>
           <t>BA - 141</t>
         </is>
       </c>
-      <c r="B440" s="1" t="inlineStr"/>
-      <c r="C440" s="1" t="inlineStr">
+      <c r="C440" t="inlineStr">
         <is>
           <t>지하주차장 전기실/발전기실 평면도</t>
         </is>
       </c>
-      <c r="D440" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E440" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F440" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G440" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H440" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I440" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J440" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K440" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>BA - 141</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>전기실/발전기실 평면도</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="inlineStr">
+      <c r="A441" t="inlineStr">
         <is>
           <t>BA - 142</t>
         </is>
       </c>
-      <c r="B441" s="1" t="inlineStr"/>
-      <c r="C441" s="1" t="inlineStr">
+      <c r="C441" t="inlineStr">
         <is>
           <t>전기실/발전기실 상부평면도</t>
         </is>
       </c>
-      <c r="D441" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E441" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F441" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G441" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H441" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I441" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J441" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K441" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>BA - 142</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>전기실/발전기실 상부평면도</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="inlineStr">
+      <c r="A442" t="inlineStr">
         <is>
           <t>BA - 143</t>
         </is>
       </c>
-      <c r="B442" s="1" t="inlineStr"/>
-      <c r="C442" s="1" t="inlineStr">
+      <c r="C442" t="inlineStr">
         <is>
           <t>전기실/발전기실 단면도-1</t>
         </is>
       </c>
-      <c r="D442" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E442" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F442" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G442" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H442" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I442" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J442" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K442" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>BA - 143</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>전기실/발전기실 단면도-1</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="inlineStr">
+      <c r="A443" t="inlineStr">
         <is>
           <t>BA - 144</t>
         </is>
       </c>
-      <c r="B443" s="1" t="inlineStr"/>
-      <c r="C443" s="1" t="inlineStr">
+      <c r="C443" t="inlineStr">
         <is>
           <t>전기실/발전기실 단면도-2</t>
         </is>
       </c>
-      <c r="D443" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E443" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F443" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G443" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H443" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I443" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J443" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K443" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>BA - 144</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>전기실/발전기실 단면도-2</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="inlineStr">
+      <c r="A444" t="inlineStr">
         <is>
           <t>BA - 145</t>
         </is>
       </c>
-      <c r="B444" s="1" t="inlineStr"/>
-      <c r="C444" s="1" t="inlineStr">
+      <c r="C444" t="inlineStr">
         <is>
           <t>전기실/발전기실 단면도-3</t>
         </is>
       </c>
-      <c r="D444" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E444" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F444" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G444" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H444" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I444" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J444" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K444" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>BA - 145</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>전기실/발전기실 단면도-3</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="inlineStr">
+      <c r="A445" t="inlineStr">
         <is>
           <t>BA - 146</t>
         </is>
       </c>
-      <c r="B445" s="1" t="inlineStr"/>
-      <c r="C445" s="1" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>전기실/발전기실 부분 단면도</t>
         </is>
       </c>
-      <c r="D445" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E445" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F445" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G445" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H445" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I445" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J445" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K445" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>BA - 146</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>전기실/발전기실 부분 단면도</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="inlineStr">
+      <c r="A446" t="inlineStr">
         <is>
           <t>BA - 147</t>
         </is>
       </c>
-      <c r="B446" s="1" t="inlineStr"/>
-      <c r="C446" s="1" t="inlineStr">
+      <c r="C446" t="inlineStr">
         <is>
           <t>발전기실 DA 상세도</t>
         </is>
@@ -23971,45 +23936,44 @@
           <t>1/100</t>
         </is>
       </c>
-      <c r="F446" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G446" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>BA - 147</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>발전기실 DA 상세도</t>
         </is>
       </c>
       <c r="H446" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="I446" s="1" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J446" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K446" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="inlineStr">
+      <c r="A447" t="inlineStr">
         <is>
           <t>BA - 148</t>
         </is>
       </c>
-      <c r="B447" s="1" t="inlineStr"/>
-      <c r="C447" s="1" t="inlineStr">
+      <c r="C447" t="inlineStr">
         <is>
           <t>전기실 DA 상세도</t>
         </is>
@@ -24024,2177 +23988,2143 @@
           <t>1/100</t>
         </is>
       </c>
-      <c r="F447" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G447" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>BA - 148</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>전기실 DA 상세도</t>
         </is>
       </c>
       <c r="H447" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="I447" s="1" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J447" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K447" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>BA-141_1BL 전기실,발전기실 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="inlineStr">
+      <c r="A448" t="inlineStr">
         <is>
           <t>BA - 151</t>
         </is>
       </c>
-      <c r="B448" s="1" t="inlineStr"/>
-      <c r="C448" s="1" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>지하주차장 펌프실/저수조 평면도</t>
         </is>
       </c>
-      <c r="D448" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E448" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F448" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G448" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H448" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I448" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J448" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K448" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>BA - 151</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 평면도</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="inlineStr">
+      <c r="A449" t="inlineStr">
         <is>
           <t>BA - 152</t>
         </is>
       </c>
-      <c r="B449" s="1" t="inlineStr"/>
-      <c r="C449" s="1" t="inlineStr">
+      <c r="C449" t="inlineStr">
         <is>
           <t>펌프실/저수조 상부평면도</t>
         </is>
       </c>
-      <c r="D449" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E449" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F449" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G449" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H449" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I449" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J449" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K449" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>BA - 152</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 상부평면도</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="inlineStr">
+      <c r="A450" t="inlineStr">
         <is>
           <t>BA - 153</t>
         </is>
       </c>
-      <c r="B450" s="1" t="inlineStr"/>
-      <c r="C450" s="1" t="inlineStr">
+      <c r="C450" t="inlineStr">
         <is>
           <t>펌프실/저수조 단면도-1</t>
         </is>
       </c>
-      <c r="D450" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E450" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F450" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G450" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H450" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I450" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J450" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K450" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>BA - 153</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 단면도-1</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="inlineStr">
+      <c r="A451" t="inlineStr">
         <is>
           <t>BA - 154</t>
         </is>
       </c>
-      <c r="B451" s="1" t="inlineStr"/>
-      <c r="C451" s="1" t="inlineStr">
+      <c r="C451" t="inlineStr">
         <is>
           <t>펌프실/저수조 단면도-2</t>
         </is>
       </c>
-      <c r="D451" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E451" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F451" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G451" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H451" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I451" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J451" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K451" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>BA - 154</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 단면도-2</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="inlineStr">
+      <c r="A452" t="inlineStr">
         <is>
           <t>BA - 155</t>
         </is>
       </c>
-      <c r="B452" s="1" t="inlineStr"/>
-      <c r="C452" s="1" t="inlineStr">
+      <c r="C452" t="inlineStr">
         <is>
           <t>펌프실/저수조 단면도-3</t>
         </is>
       </c>
-      <c r="D452" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E452" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F452" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G452" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H452" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I452" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J452" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K452" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>BA - 155</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 단면도-3</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="inlineStr">
+      <c r="A453" t="inlineStr">
         <is>
           <t>BA - 156</t>
         </is>
       </c>
-      <c r="B453" s="1" t="inlineStr"/>
-      <c r="C453" s="1" t="inlineStr">
+      <c r="C453" t="inlineStr">
         <is>
           <t>펌프실/저수조 단면도-4</t>
         </is>
       </c>
-      <c r="D453" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E453" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F453" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G453" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H453" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I453" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J453" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K453" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>BA - 156</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 단면도-4</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="inlineStr">
+      <c r="A454" t="inlineStr">
         <is>
           <t>BA - 157</t>
         </is>
       </c>
-      <c r="B454" s="1" t="inlineStr"/>
-      <c r="C454" s="1" t="inlineStr">
+      <c r="C454" t="inlineStr">
         <is>
           <t>펌프실/저수조 부분 단면도</t>
         </is>
       </c>
-      <c r="D454" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E454" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F454" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G454" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H454" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I454" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J454" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K454" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>BA - 157</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 부분 단면도</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="inlineStr">
+      <c r="A455" t="inlineStr">
         <is>
           <t>BA - 158</t>
         </is>
       </c>
-      <c r="B455" s="1" t="inlineStr"/>
-      <c r="C455" s="1" t="inlineStr">
+      <c r="C455" t="inlineStr">
         <is>
           <t>펌프실/저수조 DA 상세도</t>
         </is>
       </c>
-      <c r="D455" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E455" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F455" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G455" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H455" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I455" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J455" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K455" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>BA - 158</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>펌프실/저수조 DA 상세도</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>BA-151_1BL 펌프실,저수조 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="inlineStr">
+      <c r="A456" t="inlineStr">
         <is>
           <t>BA - 159</t>
         </is>
       </c>
-      <c r="B456" s="1" t="inlineStr"/>
-      <c r="C456" s="1" t="inlineStr">
+      <c r="C456" t="inlineStr">
         <is>
           <t>지하주차장 재활용품 보관소 상세도</t>
         </is>
       </c>
-      <c r="D456" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E456" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F456" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G456" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H456" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I456" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J456" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K456" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>BA - 159</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>지하주차장 재활용품 보관소 상세도</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>BA-159_1BL 재활용품 보관소.dwg</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="inlineStr">
+      <c r="A457" t="inlineStr">
         <is>
           <t>BA - 161</t>
         </is>
       </c>
-      <c r="B457" s="1" t="inlineStr"/>
-      <c r="C457" s="1" t="inlineStr">
+      <c r="C457" t="inlineStr">
         <is>
           <t>지하주차장 휀룸#1(급기) 상세도</t>
         </is>
       </c>
-      <c r="D457" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E457" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F457" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G457" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H457" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I457" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J457" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K457" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>BA - 161</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>휀룸#1(급기) 상세도</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="inlineStr">
+      <c r="A458" t="inlineStr">
         <is>
           <t>BA - 162</t>
         </is>
       </c>
-      <c r="B458" s="1" t="inlineStr"/>
-      <c r="C458" s="1" t="inlineStr">
+      <c r="C458" t="inlineStr">
         <is>
           <t>휀룸#2(배기) 상세도-1</t>
         </is>
       </c>
-      <c r="D458" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E458" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F458" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G458" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H458" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I458" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J458" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K458" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>BA - 162</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>휀룸#2(배기) 상세도-1</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="inlineStr">
+      <c r="A459" t="inlineStr">
         <is>
           <t>BA - 163</t>
         </is>
       </c>
-      <c r="B459" s="1" t="inlineStr"/>
-      <c r="C459" s="1" t="inlineStr">
+      <c r="C459" t="inlineStr">
         <is>
           <t>휀룸#2(배기) 상세도-2</t>
         </is>
       </c>
-      <c r="D459" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E459" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F459" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G459" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H459" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I459" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J459" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K459" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>BA - 163</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>휀룸#2(배기) 상세도-2</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="inlineStr">
+      <c r="A460" t="inlineStr">
         <is>
           <t>BA - 164</t>
         </is>
       </c>
-      <c r="B460" s="1" t="inlineStr"/>
-      <c r="C460" s="1" t="inlineStr">
+      <c r="C460" t="inlineStr">
         <is>
           <t>휀룸#3(급기) 상세도</t>
         </is>
       </c>
-      <c r="D460" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E460" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F460" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G460" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H460" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I460" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J460" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K460" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>BA - 164</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>휀룸#3(급기) 상세도</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="inlineStr">
+      <c r="A461" t="inlineStr">
         <is>
           <t>BA - 165</t>
         </is>
       </c>
-      <c r="B461" s="1" t="inlineStr"/>
-      <c r="C461" s="1" t="inlineStr">
+      <c r="C461" t="inlineStr">
         <is>
           <t>휀룸#4(배기) 상세도-1</t>
         </is>
       </c>
-      <c r="D461" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E461" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F461" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G461" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H461" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I461" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J461" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K461" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>BA - 165</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>휀룸#4(배기) 상세도-1</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="inlineStr">
+      <c r="A462" t="inlineStr">
         <is>
           <t>BA - 166</t>
         </is>
       </c>
-      <c r="B462" s="1" t="inlineStr"/>
-      <c r="C462" s="1" t="inlineStr">
+      <c r="C462" t="inlineStr">
         <is>
           <t>휀룸#4(배기) 상세도-2</t>
         </is>
       </c>
-      <c r="D462" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E462" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F462" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G462" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H462" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I462" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J462" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K462" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>BA - 166</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>휀룸#4(배기) 상세도-2</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="inlineStr">
+      <c r="A463" t="inlineStr">
         <is>
           <t>BA - 167</t>
         </is>
       </c>
-      <c r="B463" s="1" t="inlineStr"/>
-      <c r="C463" s="1" t="inlineStr">
+      <c r="C463" t="inlineStr">
         <is>
           <t>휀룸#5(급기) 상세도</t>
         </is>
       </c>
-      <c r="D463" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E463" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F463" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G463" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H463" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I463" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J463" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K463" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>BA - 167</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>휀룸#5(급기) 상세도-1</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="inlineStr">
+      <c r="A464" t="inlineStr">
         <is>
           <t>BA - 168</t>
         </is>
       </c>
-      <c r="B464" s="1" t="inlineStr"/>
-      <c r="C464" s="1" t="inlineStr">
+      <c r="C464" t="inlineStr">
         <is>
           <t>휀룸#6(배기) 상세도-1</t>
         </is>
       </c>
-      <c r="D464" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E464" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F464" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G464" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H464" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I464" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J464" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K464" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>BA - 168</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>휀룸#6(배기) 상세도-1</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="inlineStr">
+      <c r="A465" t="inlineStr">
         <is>
           <t>BA - 169</t>
         </is>
       </c>
-      <c r="B465" s="1" t="inlineStr"/>
-      <c r="C465" s="1" t="inlineStr">
+      <c r="C465" t="inlineStr">
         <is>
           <t>휀룸#6(배기) 상세도-2</t>
         </is>
       </c>
-      <c r="D465" s="1" t="inlineStr">
-        <is>
-          <t>1/50</t>
-        </is>
-      </c>
-      <c r="E465" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="F465" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G465" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H465" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I465" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J465" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K465" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>BA - 169</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>휀룸#6(배기) 상세도-2</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>1/50</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>BA-161_1BL 휀룸#1~#6 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="inlineStr">
+      <c r="A466" t="inlineStr">
         <is>
           <t>BA - 171</t>
         </is>
       </c>
-      <c r="B466" s="1" t="inlineStr"/>
-      <c r="C466" s="1" t="inlineStr">
+      <c r="C466" t="inlineStr">
         <is>
           <t>지하주차장 TOP LIGHT#1 상세도</t>
         </is>
       </c>
-      <c r="D466" s="1" t="inlineStr">
+      <c r="D466" t="inlineStr">
         <is>
           <t>1/40</t>
         </is>
       </c>
-      <c r="E466" s="1" t="inlineStr">
+      <c r="E466" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="F466" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G466" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H466" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I466" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J466" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K466" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>BA - 171</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>TOP LIGHT#1 상세도</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>1/40</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>BA-171_1BL TOP LIGHT#1~#3 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="inlineStr">
+      <c r="A467" t="inlineStr">
         <is>
           <t>BA - 172</t>
         </is>
       </c>
-      <c r="B467" s="1" t="inlineStr"/>
-      <c r="C467" s="1" t="inlineStr">
+      <c r="C467" t="inlineStr">
         <is>
           <t>TOP LIGHT#2 상세도</t>
         </is>
       </c>
-      <c r="D467" s="1" t="inlineStr">
+      <c r="D467" t="inlineStr">
         <is>
           <t>1/40</t>
         </is>
       </c>
-      <c r="E467" s="1" t="inlineStr">
+      <c r="E467" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="F467" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G467" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H467" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I467" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J467" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K467" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>BA - 172</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>TOP LIGHT#2 상세도</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>1/40</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>BA-171_1BL TOP LIGHT#1~#3 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="inlineStr">
+      <c r="A468" t="inlineStr">
         <is>
           <t>BA - 173</t>
         </is>
       </c>
-      <c r="B468" s="1" t="inlineStr"/>
-      <c r="C468" s="1" t="inlineStr">
+      <c r="C468" t="inlineStr">
         <is>
           <t>TOP LIGHT#3 상세도</t>
         </is>
       </c>
-      <c r="D468" s="1" t="inlineStr">
+      <c r="D468" t="inlineStr">
         <is>
           <t>1/40</t>
         </is>
       </c>
-      <c r="E468" s="1" t="inlineStr">
+      <c r="E468" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="F468" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G468" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H468" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I468" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J468" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K468" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>BA - 173</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>TOP LIGHT#3 상세도</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>1/40</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>BA-171_1BL TOP LIGHT#1~#3 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="inlineStr">
+      <c r="A469" t="inlineStr">
         <is>
           <t>BA - 174</t>
         </is>
       </c>
-      <c r="B469" s="1" t="inlineStr"/>
-      <c r="C469" s="1" t="inlineStr">
+      <c r="C469" t="inlineStr">
         <is>
           <t>지하주차장 창호도-1</t>
         </is>
       </c>
-      <c r="D469" s="1" t="inlineStr">
+      <c r="D469" t="inlineStr">
         <is>
           <t>1/40</t>
         </is>
       </c>
-      <c r="E469" s="1" t="inlineStr">
+      <c r="E469" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="F469" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G469" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H469" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I469" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J469" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K469" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>BA - 174</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>지하주차장 창호도-1</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>1/40</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>BA-174_1BL 지하주차장 창호도.dwg</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="inlineStr">
+      <c r="A470" t="inlineStr">
         <is>
           <t>BA - 175</t>
         </is>
       </c>
-      <c r="B470" s="1" t="inlineStr"/>
-      <c r="C470" s="1" t="inlineStr">
+      <c r="C470" t="inlineStr">
         <is>
           <t>지하주차장 창호도-2</t>
         </is>
       </c>
-      <c r="D470" s="1" t="inlineStr">
+      <c r="D470" t="inlineStr">
         <is>
           <t>1/40</t>
         </is>
       </c>
-      <c r="E470" s="1" t="inlineStr">
+      <c r="E470" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="F470" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G470" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H470" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I470" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J470" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K470" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>BA - 175</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>지하주차장 창호도-2</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>1/40</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>1/80</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>BA-174_1BL 지하주차장 창호도.dwg</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="inlineStr">
+      <c r="A471" t="inlineStr">
         <is>
           <t>BA - 181</t>
         </is>
       </c>
-      <c r="B471" s="1" t="inlineStr"/>
-      <c r="C471" s="1" t="inlineStr">
+      <c r="C471" t="inlineStr">
         <is>
           <t>지하3층(SL+61.30/SL+59.30) 배수파이프 배관도</t>
         </is>
       </c>
-      <c r="D471" s="1" t="inlineStr">
+      <c r="D471" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E471" s="1" t="inlineStr">
+      <c r="E471" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F471" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G471" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H471" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I471" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J471" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K471" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>BA - 181</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>지하3층(SL+61.30/SL+59.30) 배수파이프 배관도</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>BA-181_1BL 지하주차장 배수파이프 배관도.dwg</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="inlineStr">
+      <c r="A472" t="inlineStr">
         <is>
           <t>BA - 182</t>
         </is>
       </c>
-      <c r="B472" s="1" t="inlineStr"/>
-      <c r="C472" s="1" t="inlineStr">
+      <c r="C472" t="inlineStr">
         <is>
           <t>지하2층(SL+64.80/SL+67.00) 배수파이프 배관도</t>
         </is>
       </c>
-      <c r="D472" s="1" t="inlineStr">
+      <c r="D472" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E472" s="1" t="inlineStr">
+      <c r="E472" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F472" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G472" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H472" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I472" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J472" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K472" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>BA - 182</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>지하2층(SL+64.80/SL+67.00) 배수파이프 배관도</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>BA-181_1BL 지하주차장 배수파이프 배관도.dwg</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="inlineStr">
+      <c r="A473" t="inlineStr">
         <is>
           <t>BA - 183</t>
         </is>
       </c>
-      <c r="B473" s="1" t="inlineStr"/>
-      <c r="C473" s="1" t="inlineStr">
+      <c r="C473" t="inlineStr">
         <is>
           <t>지하1층(SL+70.50) 배수파이프 배관도</t>
         </is>
       </c>
-      <c r="D473" s="1" t="inlineStr">
+      <c r="D473" t="inlineStr">
         <is>
           <t>1/300</t>
         </is>
       </c>
-      <c r="E473" s="1" t="inlineStr">
+      <c r="E473" t="inlineStr">
         <is>
           <t>1/600</t>
         </is>
       </c>
-      <c r="F473" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G473" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H473" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I473" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J473" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K473" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>BA - 183</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>지하1층(SL+70.50) 배수파이프 배관도</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>1/600</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>BA-181_1BL 지하주차장 배수파이프 배관도.dwg</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="inlineStr">
+      <c r="A474" t="inlineStr">
         <is>
           <t>BA - 191</t>
         </is>
       </c>
-      <c r="B474" s="1" t="inlineStr"/>
-      <c r="C474" s="1" t="inlineStr">
+      <c r="C474" t="inlineStr">
         <is>
           <t>외부계단#1 상세도-1</t>
         </is>
       </c>
-      <c r="D474" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E474" s="1" t="inlineStr">
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F474" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G474" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H474" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I474" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J474" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K474" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>BA - 191</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>외부계단#1 상세도-1</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>BA-191_1BL 외부계단 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="inlineStr">
+      <c r="A475" t="inlineStr">
         <is>
           <t>BA - 192</t>
         </is>
       </c>
-      <c r="B475" s="1" t="inlineStr"/>
-      <c r="C475" s="1" t="inlineStr">
+      <c r="C475" t="inlineStr">
         <is>
           <t>외부계단#1 상세도-2</t>
         </is>
       </c>
-      <c r="D475" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E475" s="1" t="inlineStr">
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F475" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G475" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H475" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I475" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J475" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K475" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>BA - 192</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>외부계단#1 상세도-2</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>BA-191_1BL 외부계단 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="inlineStr">
+      <c r="A476" t="inlineStr">
         <is>
           <t>BA - 193</t>
         </is>
       </c>
-      <c r="B476" s="1" t="inlineStr"/>
-      <c r="C476" s="1" t="inlineStr">
+      <c r="C476" t="inlineStr">
         <is>
           <t>외부계단#2 상세도</t>
         </is>
       </c>
-      <c r="D476" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E476" s="1" t="inlineStr">
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F476" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G476" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H476" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I476" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J476" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K476" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>BA - 193</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>외부계단#2 상세도</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>BA-191_1BL 외부계단 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="inlineStr">
+      <c r="A477" t="inlineStr">
         <is>
           <t>BA - 194</t>
         </is>
       </c>
-      <c r="B477" s="1" t="inlineStr"/>
-      <c r="C477" s="1" t="inlineStr">
+      <c r="C477" t="inlineStr">
         <is>
           <t>외부계단#3 상세도</t>
         </is>
       </c>
-      <c r="D477" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E477" s="1" t="inlineStr">
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F477" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G477" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H477" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I477" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J477" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K477" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>BA - 194</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>외부계단#3 상세도</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>BA-191_1BL 외부계단 상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
         <is>
-          <t>BA - 202</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B478" s="1" t="inlineStr"/>
       <c r="C478" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D478" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E478" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F478" s="1" t="inlineStr">
+        <is>
+          <t>BA - 201</t>
+        </is>
+      </c>
+      <c r="G478" s="1" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 평·단면도-1</t>
+        </is>
+      </c>
+      <c r="H478" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I478" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J478" s="1" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K478" s="1" t="inlineStr">
+        <is>
+          <t>목록표 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>BA - 202</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>103동</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
           <t>지하주차장 부분 평면도-2</t>
         </is>
       </c>
-      <c r="D478" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E478" s="1" t="inlineStr">
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F478" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G478" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H478" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I478" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J478" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K478" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" s="1" t="inlineStr">
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>BA - 202</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 평면도-2</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>BA - 203</t>
         </is>
       </c>
-      <c r="B479" s="1" t="inlineStr"/>
-      <c r="C479" s="1" t="inlineStr">
+      <c r="C480" t="inlineStr">
         <is>
           <t>지하주차장 부분 단면도-2</t>
         </is>
       </c>
-      <c r="D479" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E479" s="1" t="inlineStr">
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F479" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G479" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H479" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I479" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J479" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K479" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" s="1" t="inlineStr">
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>BA - 203</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 단면도-2</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>BA - 204</t>
         </is>
       </c>
-      <c r="B480" s="1" t="inlineStr"/>
-      <c r="C480" s="1" t="inlineStr">
+      <c r="C481" t="inlineStr">
         <is>
           <t>지하주차장 부분 평·단면도-3</t>
         </is>
       </c>
-      <c r="D480" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E480" s="1" t="inlineStr">
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F480" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G480" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H480" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I480" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J480" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K480" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" s="1" t="inlineStr">
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>BA - 204</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 평·단면도-3</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>BA - 205</t>
         </is>
       </c>
-      <c r="B481" s="1" t="inlineStr"/>
-      <c r="C481" s="1" t="inlineStr">
+      <c r="C482" t="inlineStr">
         <is>
           <t>지하주차장 부분 평면도-4</t>
         </is>
       </c>
-      <c r="D481" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E481" s="1" t="inlineStr">
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F481" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G481" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H481" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I481" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J481" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K481" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="1" t="inlineStr">
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>BA - 205</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 평면도-4</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t>BA - 206</t>
         </is>
       </c>
-      <c r="B482" s="1" t="inlineStr"/>
-      <c r="C482" s="1" t="inlineStr">
+      <c r="C483" t="inlineStr">
         <is>
           <t>지하주차장 부분 단면도-4</t>
         </is>
       </c>
-      <c r="D482" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E482" s="1" t="inlineStr">
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F482" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G482" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H482" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I482" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J482" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K482" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" s="1" t="inlineStr">
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>BA - 206</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 단면도-4</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t>BA - 207</t>
         </is>
       </c>
-      <c r="B483" s="1" t="inlineStr"/>
-      <c r="C483" s="1" t="inlineStr">
+      <c r="C484" t="inlineStr">
         <is>
           <t>지하주차장 부분 평면도-5</t>
         </is>
       </c>
-      <c r="D483" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E483" s="1" t="inlineStr">
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F483" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G483" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H483" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I483" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J483" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K483" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="1" t="inlineStr">
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>BA - 207</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 평면도-5</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t>BA - 208</t>
         </is>
       </c>
-      <c r="B484" s="1" t="inlineStr"/>
-      <c r="C484" s="1" t="inlineStr">
+      <c r="C485" t="inlineStr">
         <is>
           <t>지하주차장 부분 단면도-5</t>
         </is>
       </c>
-      <c r="D484" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E484" s="1" t="inlineStr">
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F484" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G484" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H484" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I484" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J484" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K484" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="1" t="inlineStr">
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>BA - 208</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>지하주차장 부분 단면도-5</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>BA-201_1BL 지하주차장 부분 평단면도.dwg</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t>BA - 209</t>
         </is>
       </c>
-      <c r="B485" s="1" t="inlineStr"/>
-      <c r="C485" s="1" t="inlineStr">
+      <c r="C486" t="inlineStr">
         <is>
           <t>지하주차장  외벽상세도</t>
         </is>
       </c>
-      <c r="D485" s="1" t="inlineStr">
-        <is>
-          <t>1/100</t>
-        </is>
-      </c>
-      <c r="E485" s="1" t="inlineStr">
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
         <is>
           <t>1/200</t>
         </is>
       </c>
-      <c r="F485" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G485" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H485" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I485" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J485" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K485" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" s="1" t="inlineStr">
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>BA - 209</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>지하주차장 외벽상세도</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>BA-209_1BL 지하주차장 외벽상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t>BA - 210</t>
         </is>
       </c>
-      <c r="B486" s="1" t="inlineStr"/>
-      <c r="C486" s="1" t="inlineStr">
+      <c r="C487" t="inlineStr">
         <is>
           <t>지하주차장 잡상세도</t>
         </is>
       </c>
-      <c r="D486" s="1" t="inlineStr">
+      <c r="D487" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="E486" s="1" t="inlineStr">
+      <c r="E487" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F486" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G486" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H486" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I486" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J486" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K486" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" s="1" t="inlineStr">
-        <is>
-          <t>BA-300</t>
-        </is>
-      </c>
-      <c r="B487" s="1" t="inlineStr"/>
-      <c r="C487" s="1" t="inlineStr">
-        <is>
-          <t>관리사무소/경로당</t>
-        </is>
-      </c>
-      <c r="D487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J487" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K487" s="1" t="inlineStr">
-        <is>
-          <t>DWG 누락</t>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>BA - 210</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>지하주차장 잡상세도</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>BA-210_1BL 지하주차장 잡상세도.dwg</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>일치</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
         <is>
-          <t>BA - 301</t>
+          <t>BA-300</t>
         </is>
       </c>
       <c r="B488" s="1" t="inlineStr"/>
       <c r="C488" s="1" t="inlineStr">
         <is>
-          <t>관리사무소 평면도</t>
+          <t>관리사무소/경로당</t>
         </is>
       </c>
       <c r="D488" s="1" t="inlineStr">
         <is>
-          <t>1/60</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E488" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F488" s="1" t="inlineStr">
@@ -26231,13 +26161,13 @@
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
         <is>
-          <t>BA - 302</t>
+          <t>BA - 301</t>
         </is>
       </c>
       <c r="B489" s="1" t="inlineStr"/>
       <c r="C489" s="1" t="inlineStr">
         <is>
-          <t>경로당 평면도</t>
+          <t>관리사무소 평면도</t>
         </is>
       </c>
       <c r="D489" s="1" t="inlineStr">
@@ -26284,13 +26214,13 @@
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
         <is>
-          <t>BA - 303</t>
+          <t>BA - 302</t>
         </is>
       </c>
       <c r="B490" s="1" t="inlineStr"/>
       <c r="C490" s="1" t="inlineStr">
         <is>
-          <t>관리사무소/경로당 단면도-1</t>
+          <t>경로당 평면도</t>
         </is>
       </c>
       <c r="D490" s="1" t="inlineStr">
@@ -26337,13 +26267,13 @@
     <row r="491">
       <c r="A491" s="1" t="inlineStr">
         <is>
-          <t>BA - 304</t>
+          <t>BA - 303</t>
         </is>
       </c>
       <c r="B491" s="1" t="inlineStr"/>
       <c r="C491" s="1" t="inlineStr">
         <is>
-          <t>관리사무소/경로당 단면도-2</t>
+          <t>관리사무소/경로당 단면도-1</t>
         </is>
       </c>
       <c r="D491" s="1" t="inlineStr">
@@ -26390,13 +26320,13 @@
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
         <is>
-          <t>BA - 305</t>
+          <t>BA - 304</t>
         </is>
       </c>
       <c r="B492" s="1" t="inlineStr"/>
       <c r="C492" s="1" t="inlineStr">
         <is>
-          <t>관리사무소/경로당 정면도</t>
+          <t>관리사무소/경로당 단면도-2</t>
         </is>
       </c>
       <c r="D492" s="1" t="inlineStr">
@@ -26443,13 +26373,13 @@
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
         <is>
-          <t>BA - 306</t>
+          <t>BA - 305</t>
         </is>
       </c>
       <c r="B493" s="1" t="inlineStr"/>
       <c r="C493" s="1" t="inlineStr">
         <is>
-          <t>관리사무소/경로당 좌측면도</t>
+          <t>관리사무소/경로당 정면도</t>
         </is>
       </c>
       <c r="D493" s="1" t="inlineStr">
@@ -26496,23 +26426,23 @@
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
         <is>
-          <t>BA - 307</t>
+          <t>BA - 306</t>
         </is>
       </c>
       <c r="B494" s="1" t="inlineStr"/>
       <c r="C494" s="1" t="inlineStr">
         <is>
-          <t>관리사무소 창호일람표</t>
+          <t>관리사무소/경로당 좌측면도</t>
         </is>
       </c>
       <c r="D494" s="1" t="inlineStr">
         <is>
-          <t>1/40</t>
+          <t>1/60</t>
         </is>
       </c>
       <c r="E494" s="1" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F494" s="1" t="inlineStr">
@@ -26549,13 +26479,13 @@
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t>BA - 308</t>
+          <t>BA - 307</t>
         </is>
       </c>
       <c r="B495" s="1" t="inlineStr"/>
       <c r="C495" s="1" t="inlineStr">
         <is>
-          <t>경로당 창호일람표</t>
+          <t>관리사무소 창호일람표</t>
         </is>
       </c>
       <c r="D495" s="1" t="inlineStr">
@@ -26602,13 +26532,13 @@
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t>BA - 309</t>
+          <t>BA - 308</t>
         </is>
       </c>
       <c r="B496" s="1" t="inlineStr"/>
       <c r="C496" s="1" t="inlineStr">
         <is>
-          <t>관리사무소 화장실(남,여) 확대평면도, 전개도</t>
+          <t>경로당 창호일람표</t>
         </is>
       </c>
       <c r="D496" s="1" t="inlineStr">
@@ -26655,13 +26585,13 @@
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
         <is>
-          <t>BA - 310</t>
+          <t>BA - 309</t>
         </is>
       </c>
       <c r="B497" s="1" t="inlineStr"/>
       <c r="C497" s="1" t="inlineStr">
         <is>
-          <t>경로당 화장실(남,여) 확대평면도, 전개도</t>
+          <t>관리사무소 화장실(남,여) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D497" s="1" t="inlineStr">
@@ -26708,23 +26638,23 @@
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t>BA-400</t>
+          <t>BA - 310</t>
         </is>
       </c>
       <c r="B498" s="1" t="inlineStr"/>
       <c r="C498" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터/작은도서관</t>
+          <t>경로당 화장실(남,여) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D498" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/40</t>
         </is>
       </c>
       <c r="E498" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F498" s="1" t="inlineStr">
@@ -26761,23 +26691,23 @@
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t>BA - 401</t>
+          <t>BA-400</t>
         </is>
       </c>
       <c r="B499" s="1" t="inlineStr"/>
       <c r="C499" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터/작은도서관 평면도</t>
+          <t>다함께 돌봄센터/작은도서관</t>
         </is>
       </c>
       <c r="D499" s="1" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E499" s="1" t="inlineStr">
         <is>
-          <t>1/160</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F499" s="1" t="inlineStr">
@@ -26814,13 +26744,13 @@
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t>BA - 402</t>
+          <t>BA - 401</t>
         </is>
       </c>
       <c r="B500" s="1" t="inlineStr"/>
       <c r="C500" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터/작은도서관 지붕평면도</t>
+          <t>다함께 돌봄센터/작은도서관 평면도</t>
         </is>
       </c>
       <c r="D500" s="1" t="inlineStr">
@@ -26867,13 +26797,13 @@
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
         <is>
-          <t>BA - 403</t>
+          <t>BA - 402</t>
         </is>
       </c>
       <c r="B501" s="1" t="inlineStr"/>
       <c r="C501" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터/작은도서관 단면도-1</t>
+          <t>다함께 돌봄센터/작은도서관 지붕평면도</t>
         </is>
       </c>
       <c r="D501" s="1" t="inlineStr">
@@ -26920,13 +26850,13 @@
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
         <is>
-          <t>BA - 404</t>
+          <t>BA - 403</t>
         </is>
       </c>
       <c r="B502" s="1" t="inlineStr"/>
       <c r="C502" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터/작은도서관 단면도-2</t>
+          <t>다함께 돌봄센터/작은도서관 단면도-1</t>
         </is>
       </c>
       <c r="D502" s="1" t="inlineStr">
@@ -26973,13 +26903,13 @@
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
         <is>
-          <t>BA - 405</t>
+          <t>BA - 404</t>
         </is>
       </c>
       <c r="B503" s="1" t="inlineStr"/>
       <c r="C503" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터/작은도서관 정면도,측면도</t>
+          <t>다함께 돌봄센터/작은도서관 단면도-2</t>
         </is>
       </c>
       <c r="D503" s="1" t="inlineStr">
@@ -27026,23 +26956,23 @@
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
         <is>
-          <t>BA - 406</t>
+          <t>BA - 405</t>
         </is>
       </c>
       <c r="B504" s="1" t="inlineStr"/>
       <c r="C504" s="1" t="inlineStr">
         <is>
-          <t>다함께 돌봄센터 창호일람표</t>
+          <t>다함께 돌봄센터/작은도서관 정면도,측면도</t>
         </is>
       </c>
       <c r="D504" s="1" t="inlineStr">
         <is>
-          <t>1/40</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E504" s="1" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/160</t>
         </is>
       </c>
       <c r="F504" s="1" t="inlineStr">
@@ -27079,13 +27009,13 @@
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t>BA - 407</t>
+          <t>BA - 406</t>
         </is>
       </c>
       <c r="B505" s="1" t="inlineStr"/>
       <c r="C505" s="1" t="inlineStr">
         <is>
-          <t>작은도서관 창호일람표</t>
+          <t>다함께 돌봄센터 창호일람표</t>
         </is>
       </c>
       <c r="D505" s="1" t="inlineStr">
@@ -27132,13 +27062,13 @@
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
-          <t>BA - 408</t>
+          <t>BA - 407</t>
         </is>
       </c>
       <c r="B506" s="1" t="inlineStr"/>
       <c r="C506" s="1" t="inlineStr">
         <is>
-          <t>작은도서관 화장실(남,여) 확대평면도, 전개도</t>
+          <t>작은도서관 창호일람표</t>
         </is>
       </c>
       <c r="D506" s="1" t="inlineStr">
@@ -27185,23 +27115,23 @@
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
         <is>
-          <t>BA-500</t>
+          <t>BA - 408</t>
         </is>
       </c>
       <c r="B507" s="1" t="inlineStr"/>
       <c r="C507" s="1" t="inlineStr">
         <is>
-          <t>어린이집</t>
+          <t>작은도서관 화장실(남,여) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D507" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/40</t>
         </is>
       </c>
       <c r="E507" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F507" s="1" t="inlineStr">
@@ -27238,23 +27168,23 @@
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
         <is>
-          <t>BA - 501</t>
+          <t>BA-500</t>
         </is>
       </c>
       <c r="B508" s="1" t="inlineStr"/>
       <c r="C508" s="1" t="inlineStr">
         <is>
-          <t>어린이집 평면도</t>
+          <t>어린이집</t>
         </is>
       </c>
       <c r="D508" s="1" t="inlineStr">
         <is>
-          <t>1/60</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E508" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F508" s="1" t="inlineStr">
@@ -27291,13 +27221,13 @@
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
         <is>
-          <t>BA - 502</t>
+          <t>BA - 501</t>
         </is>
       </c>
       <c r="B509" s="1" t="inlineStr"/>
       <c r="C509" s="1" t="inlineStr">
         <is>
-          <t>어린이집 지붕 평면도</t>
+          <t>어린이집 평면도</t>
         </is>
       </c>
       <c r="D509" s="1" t="inlineStr">
@@ -27344,13 +27274,13 @@
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
         <is>
-          <t>BA - 503</t>
+          <t>BA - 502</t>
         </is>
       </c>
       <c r="B510" s="1" t="inlineStr"/>
       <c r="C510" s="1" t="inlineStr">
         <is>
-          <t>어린이집 단면도</t>
+          <t>어린이집 지붕 평면도</t>
         </is>
       </c>
       <c r="D510" s="1" t="inlineStr">
@@ -27397,13 +27327,13 @@
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
         <is>
-          <t>BA - 504</t>
+          <t>BA - 503</t>
         </is>
       </c>
       <c r="B511" s="1" t="inlineStr"/>
       <c r="C511" s="1" t="inlineStr">
         <is>
-          <t>어린이집 정면도, 배면도</t>
+          <t>어린이집 단면도</t>
         </is>
       </c>
       <c r="D511" s="1" t="inlineStr">
@@ -27450,13 +27380,13 @@
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t>BA - 505</t>
+          <t>BA - 504</t>
         </is>
       </c>
       <c r="B512" s="1" t="inlineStr"/>
       <c r="C512" s="1" t="inlineStr">
         <is>
-          <t>어린이집 좌측면도, 우측면도</t>
+          <t>어린이집 정면도, 배면도</t>
         </is>
       </c>
       <c r="D512" s="1" t="inlineStr">
@@ -27503,23 +27433,23 @@
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
         <is>
-          <t>BA - 506</t>
+          <t>BA - 505</t>
         </is>
       </c>
       <c r="B513" s="1" t="inlineStr"/>
       <c r="C513" s="1" t="inlineStr">
         <is>
-          <t>어린이집 창호일람표-1</t>
+          <t>어린이집 좌측면도, 우측면도</t>
         </is>
       </c>
       <c r="D513" s="1" t="inlineStr">
         <is>
-          <t>1/40</t>
+          <t>1/60</t>
         </is>
       </c>
       <c r="E513" s="1" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F513" s="1" t="inlineStr">
@@ -27556,13 +27486,13 @@
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
         <is>
-          <t>BA - 507</t>
+          <t>BA - 506</t>
         </is>
       </c>
       <c r="B514" s="1" t="inlineStr"/>
       <c r="C514" s="1" t="inlineStr">
         <is>
-          <t>어린이집 창호일람표-2</t>
+          <t>어린이집 창호일람표-1</t>
         </is>
       </c>
       <c r="D514" s="1" t="inlineStr">
@@ -27609,23 +27539,23 @@
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
         <is>
-          <t>BA - 508</t>
+          <t>BA - 507</t>
         </is>
       </c>
       <c r="B515" s="1" t="inlineStr"/>
       <c r="C515" s="1" t="inlineStr">
         <is>
-          <t>유 , 2 확대평면도, 전개도</t>
+          <t>어린이집 창호일람표-2</t>
         </is>
       </c>
       <c r="D515" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/40</t>
         </is>
       </c>
       <c r="E515" s="1" t="inlineStr">
         <is>
-          <t>1/40</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F515" s="1" t="inlineStr">
@@ -27662,23 +27592,23 @@
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
         <is>
-          <t>BA - 509</t>
+          <t>BA - 508</t>
         </is>
       </c>
       <c r="B516" s="1" t="inlineStr"/>
       <c r="C516" s="1" t="inlineStr">
         <is>
-          <t>유아샤워실 확대평면도, 전개도</t>
+          <t>유 , 2 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D516" s="1" t="inlineStr">
         <is>
+          <t>1/2</t>
+        </is>
+      </c>
+      <c r="E516" s="1" t="inlineStr">
+        <is>
           <t>1/40</t>
-        </is>
-      </c>
-      <c r="E516" s="1" t="inlineStr">
-        <is>
-          <t>1/80</t>
         </is>
       </c>
       <c r="F516" s="1" t="inlineStr">
@@ -27715,13 +27645,13 @@
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
         <is>
-          <t>BA - 510</t>
+          <t>BA - 509</t>
         </is>
       </c>
       <c r="B517" s="1" t="inlineStr"/>
       <c r="C517" s="1" t="inlineStr">
         <is>
-          <t>어린이집 화장실(남,여) 확대평면도, 전개도</t>
+          <t>유아샤워실 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D517" s="1" t="inlineStr">
@@ -27768,23 +27698,23 @@
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
         <is>
-          <t>BA - 601</t>
+          <t>BA - 510</t>
         </is>
       </c>
       <c r="B518" s="1" t="inlineStr"/>
       <c r="C518" s="1" t="inlineStr">
         <is>
-          <t>영구저류조 평면도</t>
+          <t>어린이집 화장실(남,여) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D518" s="1" t="inlineStr">
         <is>
+          <t>1/40</t>
+        </is>
+      </c>
+      <c r="E518" s="1" t="inlineStr">
+        <is>
           <t>1/80</t>
-        </is>
-      </c>
-      <c r="E518" s="1" t="inlineStr">
-        <is>
-          <t>1/160</t>
         </is>
       </c>
       <c r="F518" s="1" t="inlineStr">
@@ -27821,13 +27751,13 @@
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
         <is>
-          <t>BA - 602</t>
+          <t>BA - 601</t>
         </is>
       </c>
       <c r="B519" s="1" t="inlineStr"/>
       <c r="C519" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 PIT 평면도</t>
+          <t>영구저류조 평면도</t>
         </is>
       </c>
       <c r="D519" s="1" t="inlineStr">
@@ -27874,13 +27804,13 @@
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t>BA - 603</t>
+          <t>BA - 602</t>
         </is>
       </c>
       <c r="B520" s="1" t="inlineStr"/>
       <c r="C520" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 평면도</t>
+          <t>주민회의소/청소년쉼터 PIT 평면도</t>
         </is>
       </c>
       <c r="D520" s="1" t="inlineStr">
@@ -27927,13 +27857,13 @@
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
         <is>
-          <t>BA - 604</t>
+          <t>BA - 603</t>
         </is>
       </c>
       <c r="B521" s="1" t="inlineStr"/>
       <c r="C521" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 지붕평면도</t>
+          <t>주민회의소/청소년쉼터 평면도</t>
         </is>
       </c>
       <c r="D521" s="1" t="inlineStr">
@@ -27980,13 +27910,13 @@
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
         <is>
-          <t>BA - 605</t>
+          <t>BA - 604</t>
         </is>
       </c>
       <c r="B522" s="1" t="inlineStr"/>
       <c r="C522" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터/영구저류조 단면도</t>
+          <t>주민회의소/청소년쉼터 지붕평면도</t>
         </is>
       </c>
       <c r="D522" s="1" t="inlineStr">
@@ -28033,13 +27963,13 @@
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
         <is>
-          <t>BA - 606</t>
+          <t>BA - 605</t>
         </is>
       </c>
       <c r="B523" s="1" t="inlineStr"/>
       <c r="C523" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 정면도, 좌측면도</t>
+          <t>주민회의소/청소년쉼터/영구저류조 단면도</t>
         </is>
       </c>
       <c r="D523" s="1" t="inlineStr">
@@ -28086,23 +28016,23 @@
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
         <is>
-          <t>BA - 607</t>
+          <t>BA - 606</t>
         </is>
       </c>
       <c r="B524" s="1" t="inlineStr"/>
       <c r="C524" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 창호일람표-1</t>
+          <t>주민회의소/청소년쉼터 정면도, 좌측면도</t>
         </is>
       </c>
       <c r="D524" s="1" t="inlineStr">
         <is>
-          <t>1/40</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="E524" s="1" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/160</t>
         </is>
       </c>
       <c r="F524" s="1" t="inlineStr">
@@ -28139,13 +28069,13 @@
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
         <is>
-          <t>BA - 608</t>
+          <t>BA - 607</t>
         </is>
       </c>
       <c r="B525" s="1" t="inlineStr"/>
       <c r="C525" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 창호일람표-2</t>
+          <t>주민회의소/청소년쉼터 창호일람표-1</t>
         </is>
       </c>
       <c r="D525" s="1" t="inlineStr">
@@ -28192,13 +28122,13 @@
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
         <is>
-          <t>BA - 609</t>
+          <t>BA - 608</t>
         </is>
       </c>
       <c r="B526" s="1" t="inlineStr"/>
       <c r="C526" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 화장실(여) 확대평면도, 전개도</t>
+          <t>주민회의소/청소년쉼터 창호일람표-2</t>
         </is>
       </c>
       <c r="D526" s="1" t="inlineStr">
@@ -28245,13 +28175,13 @@
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
         <is>
-          <t>BA - 610</t>
+          <t>BA - 609</t>
         </is>
       </c>
       <c r="B527" s="1" t="inlineStr"/>
       <c r="C527" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 화장실(남) 확대평면도, 전개도</t>
+          <t>주민회의소/청소년쉼터 화장실(여) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D527" s="1" t="inlineStr">
@@ -28298,13 +28228,13 @@
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
         <is>
-          <t>BA - 611</t>
+          <t>BA - 610</t>
         </is>
       </c>
       <c r="B528" s="1" t="inlineStr"/>
       <c r="C528" s="1" t="inlineStr">
         <is>
-          <t>주민회의소/청소년쉼터 장애인화장실(남,여) 확대평면도, 전개도</t>
+          <t>주민회의소/청소년쉼터 화장실(남) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D528" s="1" t="inlineStr">
@@ -28351,23 +28281,23 @@
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
         <is>
-          <t>BA-700</t>
+          <t>BA - 611</t>
         </is>
       </c>
       <c r="B529" s="1" t="inlineStr"/>
       <c r="C529" s="1" t="inlineStr">
         <is>
-          <t>키즈스테이션/경비실</t>
+          <t>주민회의소/청소년쉼터 장애인화장실(남,여) 확대평면도, 전개도</t>
         </is>
       </c>
       <c r="D529" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/40</t>
         </is>
       </c>
       <c r="E529" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F529" s="1" t="inlineStr">
@@ -28404,23 +28334,23 @@
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
         <is>
-          <t>BA - 701</t>
+          <t>BA-700</t>
         </is>
       </c>
       <c r="B530" s="1" t="inlineStr"/>
       <c r="C530" s="1" t="inlineStr">
         <is>
-          <t>키즈스테이션/통합경비실 평면도 / 지붕평면도</t>
+          <t>키즈스테이션/경비실</t>
         </is>
       </c>
       <c r="D530" s="1" t="inlineStr">
         <is>
-          <t>1/60</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E530" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F530" s="1" t="inlineStr">
@@ -28457,13 +28387,13 @@
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
         <is>
-          <t>BA - 702</t>
+          <t>BA - 701</t>
         </is>
       </c>
       <c r="B531" s="1" t="inlineStr"/>
       <c r="C531" s="1" t="inlineStr">
         <is>
-          <t>키즈스테이션/통합경비실 단면도</t>
+          <t>키즈스테이션/통합경비실 평면도 / 지붕평면도</t>
         </is>
       </c>
       <c r="D531" s="1" t="inlineStr">
@@ -28510,13 +28440,13 @@
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
         <is>
-          <t>BA - 703</t>
+          <t>BA - 702</t>
         </is>
       </c>
       <c r="B532" s="1" t="inlineStr"/>
       <c r="C532" s="1" t="inlineStr">
         <is>
-          <t>키즈스테이션/통합경비실 정면도 / 우측면도</t>
+          <t>키즈스테이션/통합경비실 단면도</t>
         </is>
       </c>
       <c r="D532" s="1" t="inlineStr">
@@ -28563,23 +28493,23 @@
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
         <is>
-          <t>BA - 704</t>
+          <t>BA - 703</t>
         </is>
       </c>
       <c r="B533" s="1" t="inlineStr"/>
       <c r="C533" s="1" t="inlineStr">
         <is>
-          <t>키즈스테이션/통합경비실 창호일람표-1</t>
+          <t>키즈스테이션/통합경비실 정면도 / 우측면도</t>
         </is>
       </c>
       <c r="D533" s="1" t="inlineStr">
         <is>
-          <t>1/40</t>
+          <t>1/60</t>
         </is>
       </c>
       <c r="E533" s="1" t="inlineStr">
         <is>
-          <t>1/80</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F533" s="1" t="inlineStr">
@@ -28616,13 +28546,13 @@
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
         <is>
-          <t>BA - 705</t>
+          <t>BA - 704</t>
         </is>
       </c>
       <c r="B534" s="1" t="inlineStr"/>
       <c r="C534" s="1" t="inlineStr">
         <is>
-          <t>키즈스테이션/통합경비실 창호일람표-2</t>
+          <t>키즈스테이션/통합경비실 창호일람표-1</t>
         </is>
       </c>
       <c r="D534" s="1" t="inlineStr">
@@ -28669,23 +28599,23 @@
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
         <is>
-          <t>BA-800</t>
+          <t>BA - 705</t>
         </is>
       </c>
       <c r="B535" s="1" t="inlineStr"/>
       <c r="C535" s="1" t="inlineStr">
         <is>
-          <t>근로자 휴게실</t>
+          <t>키즈스테이션/통합경비실 창호일람표-2</t>
         </is>
       </c>
       <c r="D535" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/40</t>
         </is>
       </c>
       <c r="E535" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F535" s="1" t="inlineStr">
@@ -28722,23 +28652,23 @@
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
         <is>
-          <t>BA - 801</t>
+          <t>BA-800</t>
         </is>
       </c>
       <c r="B536" s="1" t="inlineStr"/>
       <c r="C536" s="1" t="inlineStr">
         <is>
-          <t>근로자 휴게실 평면도 / 입면도 / 단면도</t>
+          <t>근로자 휴게실</t>
         </is>
       </c>
       <c r="D536" s="1" t="inlineStr">
         <is>
-          <t>1/60</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E536" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F536" s="1" t="inlineStr">
@@ -28775,51 +28705,104 @@
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
         <is>
-          <t>BA - 802</t>
+          <t>BA - 801</t>
         </is>
       </c>
       <c r="B537" s="1" t="inlineStr"/>
       <c r="C537" s="1" t="inlineStr">
         <is>
+          <t>근로자 휴게실 평면도 / 입면도 / 단면도</t>
+        </is>
+      </c>
+      <c r="D537" s="1" t="inlineStr">
+        <is>
+          <t>1/60</t>
+        </is>
+      </c>
+      <c r="E537" s="1" t="inlineStr">
+        <is>
+          <t>1/120</t>
+        </is>
+      </c>
+      <c r="F537" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G537" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H537" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I537" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J537" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K537" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>BA - 802</t>
+        </is>
+      </c>
+      <c r="B538" s="1" t="inlineStr"/>
+      <c r="C538" s="1" t="inlineStr">
+        <is>
           <t>근로자 휴게실 창호일람표</t>
         </is>
       </c>
-      <c r="D537" s="1" t="inlineStr">
+      <c r="D538" s="1" t="inlineStr">
         <is>
           <t>1/40</t>
         </is>
       </c>
-      <c r="E537" s="1" t="inlineStr">
+      <c r="E538" s="1" t="inlineStr">
         <is>
           <t>1/80</t>
         </is>
       </c>
-      <c r="F537" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G537" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H537" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I537" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J537" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K537" s="1" t="inlineStr">
+      <c r="F538" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G538" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H538" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I538" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J538" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K538" s="1" t="inlineStr">
         <is>
           <t>DWG 누락</t>
         </is>

--- a/도면검토리포트_최종.xlsx
+++ b/도면검토리포트_최종.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L246"/>
+  <dimension ref="A1:L274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,19 +486,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A0- 001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>109동</t>
-        </is>
-      </c>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>A-000</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>A0 건축 - 공 통 도면목록표-1</t>
+          <t>건축계획</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -508,230 +504,239 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>A- 001</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>도면목록표-1</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>A0 - 001</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>도면목록표-1</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>A- 002</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>도면목록표-2</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>도곽,목록표 블럭깬거.dwg</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A0- 002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>도면목록표-2</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>A- 003</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>도면목록표-3</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A0 - 002</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>도면목록표-2</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>A- 011</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>위치도 및 주변현황 분석도</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>도곽,목록표 블럭깬거.dwg</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A0- 003</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>도면목록표-3</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>A0 - 003</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>도면목록표-3</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>도곽,목록표 블럭깬거.dwg</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A0- 004</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>도면목록표-4</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>A0 - 004</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>도면목록표-4</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>도곽,목록표 블럭깬거.dwg</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>일치</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A0- 005</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>도면목록표-5</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>A0 - 005</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>도면목록표-5</t>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
@@ -739,27 +744,27 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>도곽,목록표 블럭깬거.dwg</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>일치</t>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A0- 016</t>
+          <t>A- 012</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>광역적 현황 분석</t>
+          <t>지구단위계획 결정도</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -807,13 +812,13 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>A0- 017</t>
+          <t>A- 013</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr"/>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>위치도 및 주변현황 분석도</t>
+          <t>설계개요</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -861,13 +866,13 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>A0- 018</t>
+          <t>A- 014</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr"/>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>정비구역 결정도 (환지도)</t>
+          <t>동별개요</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -915,13 +920,13 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>A0- 019</t>
+          <t>A- 015</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>대지구적도</t>
+          <t>조감도</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -931,7 +936,7 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -969,13 +974,13 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>A0- 020</t>
+          <t>A- 016</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr"/>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>교통처리계획도</t>
+          <t>교통종합개선안도</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -1023,13 +1028,13 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>A0- 021</t>
+          <t>A- 021</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr"/>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>조감도</t>
+          <t>단지배치도(CG)</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -1039,7 +1044,7 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1200</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -1077,13 +1082,13 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>A0- 022</t>
+          <t>A- 022</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr"/>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>단지배치도(CG)</t>
+          <t>단지배치도</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -1131,13 +1136,13 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>A0- 023</t>
+          <t>A- 023</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr"/>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>설계개요</t>
+          <t>지반층배치도</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -1147,7 +1152,7 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -1185,13 +1190,13 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>A0- 024</t>
+          <t>A- 024</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr"/>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>동별개요</t>
+          <t>인동거리 배치도</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -1201,7 +1206,7 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -1239,13 +1244,13 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>A0- 025</t>
+          <t>A- 025</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr"/>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>단지배치도</t>
+          <t>대지 구적도</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -1293,13 +1298,13 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>A0- 026</t>
+          <t>A- 026</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>지반층 배치도</t>
+          <t>대지 종횡단면도-1</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -1347,13 +1352,13 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>A0- 027</t>
+          <t>A- 027</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr"/>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>인동거리 배치도</t>
+          <t>대지 종횡단면도-2</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -1401,13 +1406,13 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>A0- 028</t>
+          <t>A- 028</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr"/>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>대지종횡단면도-1</t>
+          <t>지하2층 교통체계도 (+97.00)</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -1417,7 +1422,7 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>1/800</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -1455,13 +1460,13 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>A0- 029</t>
+          <t>A- 029</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr"/>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>대지종횡단면도-2</t>
+          <t>지하1층 교통체계도 (+100.40)</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1471,7 +1476,7 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>1/800</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
@@ -1509,13 +1514,13 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>A0- 031</t>
+          <t>A- 030</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr"/>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>지하차량 교통체계도-1</t>
+          <t>비상차량 동선계획도</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1525,7 +1530,7 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>1/1500</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -1563,13 +1568,13 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>A0- 032</t>
+          <t>A- 031</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr"/>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>지하차량 교통체계도-2</t>
+          <t>장애인 편의시설 설치계획도-1</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -1579,7 +1584,7 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>1/1500</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -1617,13 +1622,13 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>A0- 033</t>
+          <t>A- 032</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr"/>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>비상차량 동선계획도</t>
+          <t>장애인 편의시설 설치계획도-2</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1671,13 +1676,13 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>A0- 041</t>
+          <t>A- 033</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr"/>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-1</t>
+          <t>장애인 편의시설 설치계획도-3</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1725,13 +1730,13 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>A0- 042</t>
+          <t>A- 034</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr"/>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-2</t>
+          <t>장애인 편의시설 설치계획도-4</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1779,13 +1784,13 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>A0- 043</t>
+          <t>A- 035</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr"/>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-3</t>
+          <t>장애인 편의시설 상세도-1</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1795,7 +1800,7 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -1833,13 +1838,13 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>A0- 044</t>
+          <t>A- 036</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr"/>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-4</t>
+          <t>장애인 편의시설 상세도-2</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1849,7 +1854,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -1887,13 +1892,13 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>A0- 045</t>
+          <t>A- 037</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-5</t>
+          <t>장애인 편의시설 상세도-3</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1903,7 +1908,7 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
@@ -1941,13 +1946,13 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>A0- 046</t>
+          <t>A- 038</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-6</t>
+          <t>장애인 편의시설 상세도-4</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1957,7 +1962,7 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -1995,13 +2000,13 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>A0- 047</t>
+          <t>A- 039</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr"/>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 설치 계획도-7(부대시설)</t>
+          <t>장애인 편의시설 상세도-5</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -2011,7 +2016,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -2049,13 +2054,13 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>A0- 048</t>
+          <t>A- 040</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-1</t>
+          <t>장애인 편의시설 상세도-6</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -2103,13 +2108,13 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>A0- 049</t>
+          <t>A- 041</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-2</t>
+          <t>장애인 편의시설 상세도-7</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -2157,13 +2162,13 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>A0- 050</t>
+          <t>A- 042</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-3</t>
+          <t>방화구획 계획도-1 (지하 2층)</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -2173,7 +2178,7 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
@@ -2211,13 +2216,13 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>A0- 051</t>
+          <t>A- 043</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-4</t>
+          <t>방화구획 계획도-2 (지하 1층)</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
@@ -2227,7 +2232,7 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
@@ -2265,13 +2270,13 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>A0- 052</t>
+          <t>A- 044</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-5</t>
+          <t>방화구획 계획도-3 (지상 1층)</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -2281,7 +2286,7 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
@@ -2319,13 +2324,13 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>A0- 053</t>
+          <t>A- 045</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-6</t>
+          <t>방화구획 계획도-4 (기준층)</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -2335,7 +2340,7 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -2373,13 +2378,13 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>A0- 054</t>
+          <t>A- 046</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>장애인 편의시설 계획도-7</t>
+          <t>실내재료마감표-1</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -2427,13 +2432,13 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>A0- 061</t>
+          <t>A- 047</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>방화구획 계획도-1</t>
+          <t>실내재료마감표-2</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -2443,7 +2448,7 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -2481,13 +2486,13 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>A0- 062</t>
+          <t>A- 048</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>방화구획 계획도-2</t>
+          <t>실내재료마감표-3</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -2497,7 +2502,7 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
@@ -2535,13 +2540,13 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>A0- 063</t>
+          <t>A- 051</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>방화구획 계획도-3</t>
+          <t>형별 성능 내역 상세도-1 (주거)</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -2551,7 +2556,7 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
@@ -2589,13 +2594,13 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>A0- 064</t>
+          <t>A- 052</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>방화구획 계획도-4</t>
+          <t>형별 성능 내역 상세도-2 (주거)</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -2605,7 +2610,7 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
@@ -2643,13 +2648,13 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>A0- 065</t>
+          <t>A- 053</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>방화구획 계획도-5</t>
+          <t>형별 성능 내역 상세도-3 (주거)</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -2659,7 +2664,7 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>1/1000</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -2697,13 +2702,13 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>A0- 071</t>
+          <t>A- 054</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>실내재료마감표-1</t>
+          <t>형별 성능 내역 상세도-1 (비주거)</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -2751,13 +2756,13 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>A0- 072</t>
+          <t>A- 055</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>실내재료마감표-2</t>
+          <t>형별 성능 내역 상세도-2 (비주거)</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -2805,13 +2810,13 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>A0- 073</t>
+          <t>A- 056</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>실내재료마감표-3</t>
+          <t>형별 성능 내역 상세도-3 (비주거)</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -2859,13 +2864,13 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>A0- 074</t>
+          <t>A- 057</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>실내재료마감표-4</t>
+          <t>형별 성능 내역 상세도-4 (비주거)</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -2913,13 +2918,13 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>A0- 081</t>
+          <t>A- 061</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-1</t>
+          <t>59㎡-A형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -2929,7 +2934,7 @@
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
@@ -2967,13 +2972,13 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>A0- 082</t>
+          <t>A- 062</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-2</t>
+          <t>59㎡-B형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -2983,7 +2988,7 @@
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -3021,13 +3026,13 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>A0- 083</t>
+          <t>A- 063</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-3</t>
+          <t>84㎡-A형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
@@ -3037,7 +3042,7 @@
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -3075,13 +3080,13 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>A0- 084</t>
+          <t>A- 064</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-4</t>
+          <t>84㎡-B형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -3091,7 +3096,7 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -3129,13 +3134,13 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>A0- 085</t>
+          <t>A- 065</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr"/>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-5</t>
+          <t>84㎡-C형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
@@ -3145,7 +3150,7 @@
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/150</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
@@ -3183,13 +3188,13 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>A0- 086</t>
+          <t>A- 066</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr"/>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-6</t>
+          <t>84㎡-D형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -3199,7 +3204,7 @@
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/150</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
@@ -3237,13 +3242,13 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>A0- 087</t>
+          <t>A- 067</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr"/>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-7</t>
+          <t>111㎡형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -3253,7 +3258,7 @@
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/150</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -3291,13 +3296,13 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>A0- 088</t>
+          <t>A- 068</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr"/>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-8</t>
+          <t>118㎡형 단위세대 면적산출근거표</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -3307,7 +3312,7 @@
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/150</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -3345,13 +3350,13 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>A0- 089</t>
+          <t>A- 071</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr"/>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>형별 성능 내역 상세도-9</t>
+          <t>코어 면적산출근거표-1</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -3361,7 +3366,7 @@
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/400</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -3399,13 +3404,13 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>A1- 001</t>
+          <t>A- 072</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr"/>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>단위세대 84㎡A형 단위세대 평면도 (기본형)</t>
+          <t>코어 면적산출근거표-2</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -3415,7 +3420,7 @@
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/400</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -3453,13 +3458,13 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>A1- 002</t>
+          <t>A- 073</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr"/>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>단위세대 평면도 (확장형)</t>
+          <t>코어 면적산출근거표-3</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -3469,7 +3474,7 @@
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/400</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -3507,13 +3512,13 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>A1- 003</t>
+          <t>A- 074</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr"/>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>84㎡B형 단위세대 평면도 (기본형)</t>
+          <t>코어 면적산출근거표-4</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -3523,7 +3528,7 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/400</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -3561,13 +3566,13 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>A1- 004</t>
+          <t>A- 075</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr"/>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>단위세대 평면도 (확장형)</t>
+          <t>코어 면적산출근거표-5</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -3577,7 +3582,7 @@
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/400</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -3615,13 +3620,13 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>A1- 005</t>
+          <t>A- 076</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr"/>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>84㎡C형 단위세대 평면도 (기본형)</t>
+          <t>동 면적산출근거표-1</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -3631,7 +3636,7 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -3669,13 +3674,13 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>A1- 006</t>
+          <t>A- 077</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr"/>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>단위세대 평면도 (확장형)</t>
+          <t>동 면적산출근거표-2</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -3685,7 +3690,7 @@
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -3723,13 +3728,13 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>A1- 007</t>
+          <t>A- 078</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr"/>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>84㎡D형 단위세대 평면도 (기본형)</t>
+          <t>동 면적산출근거표-3</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
@@ -3739,7 +3744,7 @@
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -3777,13 +3782,13 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>A1- 008</t>
+          <t>A- 079</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr"/>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>단위세대 평면도 (확장형)</t>
+          <t>동 면적산출근거표-4</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -3793,7 +3798,7 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
@@ -3831,13 +3836,13 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>A1- 009</t>
+          <t>A- 080</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr"/>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>105㎡A형 단위세대 평면도 (기본형)</t>
+          <t>동 면적산출근거표-5</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -3847,7 +3852,7 @@
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
@@ -3885,13 +3890,13 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>A1- 010</t>
+          <t>A- 081</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr"/>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>단위세대 평면도 (확장형)</t>
+          <t>지하주차장 면적산출근거표-1</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -3901,7 +3906,7 @@
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
@@ -3939,13 +3944,13 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>A1- 021</t>
+          <t>A- 082</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr"/>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>84㎡A형 주단면도(확장형)</t>
+          <t>지하주차장 면적산출근거표-2</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
@@ -3955,7 +3960,7 @@
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
@@ -3993,13 +3998,13 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>A1- 022</t>
+          <t>A- 083</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr"/>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>84㎡B형 주단면도(확장형)</t>
+          <t>부대복리시설 면적산출근거표-1</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
@@ -4009,7 +4014,7 @@
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -4047,13 +4052,13 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>A1- 023</t>
+          <t>A- 084</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr"/>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>84㎡C형 주단면도(확장형)</t>
+          <t>부대복리시설 면적산출근거표-2</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
@@ -4063,7 +4068,7 @@
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -4101,13 +4106,13 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>A1- 024</t>
+          <t>A- 085</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr"/>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>84㎡D형 주단면도(확장형)</t>
+          <t>근린생활시설 면적산출근거표-1</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -4117,7 +4122,7 @@
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
@@ -4155,13 +4160,13 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>A1- 025</t>
+          <t>A- 086</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr"/>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>105㎡A형 주단면도(확장형)</t>
+          <t>근린생활시설 면적산출근거표-2</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
@@ -4171,7 +4176,7 @@
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
@@ -4209,13 +4214,13 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>A1- 031</t>
+          <t>A- 091</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr"/>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>84㎡A형 단위세대 창호일람표 (기본형)</t>
+          <t>지하층 인정 산출도-1</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -4225,7 +4230,7 @@
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
@@ -4263,13 +4268,13 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>A1- 032</t>
+          <t>A- 092</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr"/>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>단위세대 창호일람표 (확장형)</t>
+          <t>지하층 인정 산출도-2</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -4279,7 +4284,7 @@
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/600</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
@@ -4317,13 +4322,13 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>A1- 033</t>
+          <t>A-100</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr"/>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>84㎡B형 단위세대 창호일람표 (기본형)</t>
+          <t>단위세대</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
@@ -4333,7 +4338,7 @@
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
@@ -4371,13 +4376,13 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>A1- 034</t>
+          <t>A- 101</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr"/>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>단위세대 창호일람표 (확장형)</t>
+          <t>59㎡-A형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
@@ -4387,7 +4392,7 @@
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
@@ -4425,13 +4430,13 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>A1- 035</t>
+          <t>A- 102</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr"/>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>84㎡C형 단위세대 창호일람표 (기본형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -4441,7 +4446,7 @@
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
@@ -4479,13 +4484,13 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>A1- 036</t>
+          <t>A- 103</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr"/>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>단위세대 창호일람표 (확장형)</t>
+          <t>59㎡-B형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -4495,7 +4500,7 @@
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
@@ -4533,13 +4538,13 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>A1- 037</t>
+          <t>A- 104</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr"/>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>84㎡D형 단위세대 창호일람표 (기본형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
@@ -4549,7 +4554,7 @@
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
@@ -4587,13 +4592,13 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>A1- 038</t>
+          <t>A- 105</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr"/>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>단위세대 창호일람표 (확장형)</t>
+          <t>84㎡-A형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
@@ -4603,7 +4608,7 @@
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
@@ -4641,13 +4646,13 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>A1- 039</t>
+          <t>A- 106</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr"/>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>105㎡A형 단위세대 창호일람표 (기본형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -4657,7 +4662,7 @@
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
@@ -4695,13 +4700,13 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>A1- 040</t>
+          <t>A- 107</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr"/>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>단위세대 창호일람표 (확장형)</t>
+          <t>84㎡-B형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -4711,7 +4716,7 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
@@ -4749,13 +4754,13 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>A1- 050</t>
+          <t>A- 108</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr"/>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>공용 창호일람표</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -4765,7 +4770,7 @@
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
@@ -4803,13 +4808,13 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>A1- 051</t>
+          <t>A- 109</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr"/>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>84㎡A형 단위세대 결로방지,단열,방수 평면도 (기본형)</t>
+          <t>84㎡-C형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
@@ -4819,7 +4824,7 @@
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
@@ -4857,13 +4862,13 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>A1- 052</t>
+          <t>A- 110</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr"/>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>단위세대 결로방지,단열,방수 평면도 (확장형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
@@ -4873,7 +4878,7 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
@@ -4911,13 +4916,13 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>A1- 053</t>
+          <t>A- 111</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr"/>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>84㎡B형 단위세대 결로방지,단열,방수 평면도 (기본형)</t>
+          <t>84㎡-D형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
@@ -4927,7 +4932,7 @@
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
@@ -4965,13 +4970,13 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>A1- 054</t>
+          <t>A- 112</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr"/>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>단위세대 결로방지,단열,방수 평면도 (확장형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
@@ -4981,7 +4986,7 @@
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
@@ -5019,13 +5024,13 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>A1- 055</t>
+          <t>A- 113</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr"/>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>84㎡C형 단위세대 결로방지,단열,방수 평면도 (기본형)</t>
+          <t>111㎡형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
@@ -5035,7 +5040,7 @@
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
@@ -5073,13 +5078,13 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>A1- 056</t>
+          <t>A- 114</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr"/>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>단위세대 결로방지,단열,방수 평면도 (확장형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
@@ -5089,7 +5094,7 @@
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
@@ -5127,13 +5132,13 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>A1- 057</t>
+          <t>A- 115</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr"/>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>84㎡D형 단위세대 결로방지,단열,방수 평면도 (기본형)</t>
+          <t>118㎡형 단위세대 평면도 (기본형)</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
@@ -5143,7 +5148,7 @@
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
@@ -5181,13 +5186,13 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>A1- 058</t>
+          <t>A- 116</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr"/>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>단위세대 결로방지,단열,방수 평면도 (확장형)</t>
+          <t>단위세대 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
@@ -5197,7 +5202,7 @@
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/80</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
@@ -5235,13 +5240,13 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>A1- 059</t>
+          <t>A- 121</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr"/>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>105㎡A형 단위세대 결로방지,단열,방수 평면도 (기본형)</t>
+          <t>59㎡-A형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
@@ -5251,7 +5256,7 @@
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
@@ -5289,13 +5294,13 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>A1- 060</t>
+          <t>A- 122</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr"/>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>단위세대 결로방지,단열,방수 평면도 (확장형)</t>
+          <t>59㎡-B형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -5305,7 +5310,7 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
@@ -5343,17 +5348,13 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>A2- 261</t>
-        </is>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>104동</t>
-        </is>
-      </c>
+          <t>A- 123</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr"/>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>지하3층 평면도</t>
+          <t>84㎡-A형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
@@ -5363,7 +5364,7 @@
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
@@ -5401,13 +5402,13 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>A2- 262</t>
+          <t>A- 124</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr"/>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>지하2층 평면도</t>
+          <t>84㎡-B형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
@@ -5417,7 +5418,7 @@
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
@@ -5455,13 +5456,13 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>A2- 263</t>
+          <t>A- 125</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr"/>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>지상1층 평면도</t>
+          <t>84㎡-C형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
@@ -5471,7 +5472,7 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
@@ -5509,13 +5510,13 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>A2- 264</t>
+          <t>A- 126</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr"/>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>지상2층 평면도</t>
+          <t>84㎡-D형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
@@ -5525,7 +5526,7 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
@@ -5563,13 +5564,13 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>A2- 265</t>
+          <t>A- 127</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr"/>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>기준층 평면도</t>
+          <t>111㎡형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
@@ -5579,7 +5580,7 @@
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
@@ -5617,13 +5618,13 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>A2- 266</t>
+          <t>A- 128</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr"/>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>26층 평면도</t>
+          <t>118㎡형 단위세대 주단면도 (확장형)</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
@@ -5633,7 +5634,7 @@
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/120</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
@@ -5671,13 +5672,13 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>A2- 267</t>
+          <t>A- 131</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr"/>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>27~29층 평면도</t>
+          <t>59㎡-A형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
@@ -5687,7 +5688,7 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
@@ -5725,13 +5726,13 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>A2- 268</t>
+          <t>A- 132</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr"/>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>지붕,옥탑,옥탑지붕 평면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
@@ -5741,7 +5742,7 @@
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
@@ -5779,13 +5780,13 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>A2- 269</t>
+          <t>A- 133</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr"/>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>입면도-정면도,우측면도</t>
+          <t>59㎡-B형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
@@ -5795,7 +5796,7 @@
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
@@ -5833,13 +5834,13 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>A2- 270</t>
+          <t>A- 134</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr"/>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>입면도-배면도,좌측면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -5849,7 +5850,7 @@
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
@@ -5887,17 +5888,13 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>A2- 281</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>105동</t>
-        </is>
-      </c>
+          <t>A- 135</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr"/>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>지하3층 평면도</t>
+          <t>84㎡-A형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
@@ -5907,7 +5904,7 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
@@ -5945,13 +5942,13 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>A2- 282</t>
+          <t>A- 136</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr"/>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>지하2층 평면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
@@ -5961,7 +5958,7 @@
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
@@ -5999,13 +5996,13 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>A2- 283</t>
+          <t>A- 137</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr"/>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>지하1층 평면도</t>
+          <t>84㎡-B형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
@@ -6015,7 +6012,7 @@
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
@@ -6053,13 +6050,13 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>A2- 284</t>
+          <t>A- 138</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr"/>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>지상1층 평면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
@@ -6069,7 +6066,7 @@
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
@@ -6107,13 +6104,13 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>A2- 285</t>
+          <t>A- 139</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr"/>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>지상2층 평면도</t>
+          <t>84㎡-C형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
@@ -6123,7 +6120,7 @@
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
@@ -6161,13 +6158,13 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>A2- 286</t>
+          <t>A- 140</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr"/>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>기준층 평면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
@@ -6177,7 +6174,7 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
@@ -6215,13 +6212,13 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>A2- 287</t>
+          <t>A- 141</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr"/>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>30층 평면도</t>
+          <t>84㎡-D형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
@@ -6231,7 +6228,7 @@
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
@@ -6269,13 +6266,13 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>A2- 288</t>
+          <t>A- 142</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr"/>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>31층 평면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
@@ -6285,7 +6282,7 @@
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
@@ -6323,13 +6320,13 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>A2- 289</t>
+          <t>A- 143</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr"/>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>지붕,옥탑,옥탑지붕 평면도</t>
+          <t>111㎡형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
@@ -6339,7 +6336,7 @@
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
@@ -6377,13 +6374,13 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>A2- 290</t>
+          <t>A- 144</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr"/>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>입면도-정면도,우측면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
@@ -6393,7 +6390,7 @@
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
@@ -6431,13 +6428,13 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>A2- 291</t>
+          <t>A- 145</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr"/>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>입면도-배면도,좌측면도</t>
+          <t>118㎡형 단위세대 창호일람표 (기본형)</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
@@ -6447,7 +6444,7 @@
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
@@ -6485,17 +6482,13 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>A2- 301</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>106동</t>
-        </is>
-      </c>
+          <t>A- 146</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr"/>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>지하2층 평면도</t>
+          <t>단위세대 창호일람표 (확장형)</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
@@ -6505,7 +6498,7 @@
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
@@ -6543,13 +6536,13 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>A2- 302</t>
+          <t>A- 147</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr"/>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t>지하1층 평면도</t>
+          <t>공용 창호일람표</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
@@ -6559,7 +6552,7 @@
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F114" s="1" t="inlineStr">
@@ -6597,13 +6590,13 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>A2- 303</t>
+          <t>A- 151</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr"/>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>지상1층 평면도</t>
+          <t>59㎡-A형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -6613,7 +6606,7 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
@@ -6651,13 +6644,13 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>A2- 304</t>
+          <t>A- 152</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr"/>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>지상2층 평면도</t>
+          <t>59㎡-B형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
@@ -6667,7 +6660,7 @@
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
@@ -6705,13 +6698,13 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>A2- 305</t>
+          <t>A- 153</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr"/>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>지상3층 평면도</t>
+          <t>84㎡-A형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
@@ -6721,7 +6714,7 @@
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
@@ -6759,13 +6752,13 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>A2- 306</t>
+          <t>A- 154</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr"/>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>지상4층 평면도</t>
+          <t>84㎡-B형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
@@ -6775,7 +6768,7 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
@@ -6813,13 +6806,13 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>A2- 307</t>
+          <t>A- 155</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr"/>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>기준층 평면도</t>
+          <t>84㎡-C형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
@@ -6829,7 +6822,7 @@
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
@@ -6867,13 +6860,13 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>A2- 308</t>
+          <t>A- 156</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr"/>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>25층 평면도</t>
+          <t>84㎡-D형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
@@ -6883,7 +6876,7 @@
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
@@ -6921,13 +6914,13 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>A2- 309</t>
+          <t>A- 157</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr"/>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>26~32층 평면도</t>
+          <t>111㎡형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
@@ -6937,7 +6930,7 @@
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
@@ -6975,13 +6968,13 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>A2- 310</t>
+          <t>A- 158</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr"/>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>지붕,옥탑,옥탑지붕 평면도</t>
+          <t>118㎡형 단위세대 단열 및 방수 평면도 (확장형)</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
@@ -6991,7 +6984,7 @@
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
@@ -7029,13 +7022,13 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>A2- 311</t>
+          <t>A-200~300</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr"/>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>입면도-정면도,우측면도</t>
+          <t>동 관련도면</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -7045,7 +7038,7 @@
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
@@ -7083,13 +7076,17 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>A2- 312</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="inlineStr"/>
+          <t>A- 201</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>101동</t>
+        </is>
+      </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>입면도-배면도,좌측면도</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
@@ -7099,7 +7096,7 @@
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
@@ -7137,17 +7134,13 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>A2- 321</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>107동</t>
-        </is>
-      </c>
+          <t>A- 202</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr"/>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>지하3층 평면도</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
@@ -7157,7 +7150,7 @@
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
@@ -7195,13 +7188,13 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>A2- 322</t>
+          <t>A- 203</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr"/>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>지하2층 평면도</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
@@ -7211,7 +7204,7 @@
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
@@ -7249,13 +7242,13 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>A2- 323</t>
+          <t>A- 204</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr"/>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>지상1층 평면도</t>
+          <t>기준층(2~26층) 평면도</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
@@ -7265,7 +7258,7 @@
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
@@ -7303,13 +7296,13 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>A2- 324</t>
+          <t>A- 205</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr"/>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>지상2층 평면도</t>
+          <t>27층 평면도</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -7319,7 +7312,7 @@
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
@@ -7357,13 +7350,13 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>A2- 325</t>
+          <t>A- 206</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr"/>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>기준층 평면도</t>
+          <t>28-29층 평면도</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
@@ -7373,7 +7366,7 @@
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
@@ -7411,13 +7404,13 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>A2- 326</t>
+          <t>A- 207</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr"/>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>19층 평면도</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
@@ -7427,7 +7420,7 @@
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
@@ -7465,13 +7458,13 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>A2- 327</t>
+          <t>A- 208</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr"/>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>20층 평면도</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
@@ -7481,7 +7474,7 @@
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
@@ -7519,13 +7512,13 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>A2- 328</t>
+          <t>A- 209</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr"/>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>21~23층 평면도</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
@@ -7535,7 +7528,7 @@
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
@@ -7573,13 +7566,13 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A2- 329</t>
+          <t>A- 210</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr"/>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>24층 평면도</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -7589,7 +7582,7 @@
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
@@ -7627,13 +7620,17 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A2- 330</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr"/>
+          <t>A- 211</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>102동</t>
+        </is>
+      </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>25~27층 평면도</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -7643,7 +7640,7 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
@@ -7681,13 +7678,13 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A2- 331</t>
+          <t>A- 212</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr"/>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>28층 평면도</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
@@ -7697,7 +7694,7 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
@@ -7735,13 +7732,13 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A2- 332</t>
+          <t>A- 213</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr"/>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>29층 평면도</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
@@ -7751,7 +7748,7 @@
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
@@ -7789,13 +7786,13 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A2- 333</t>
+          <t>A- 214</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr"/>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>지붕,옥탑,옥탑지붕 평면도</t>
+          <t>기준층(2~29층) 평면도</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
@@ -7805,7 +7802,7 @@
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
@@ -7843,13 +7840,13 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A2- 334</t>
+          <t>A- 215</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr"/>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>입면도-정면도,우측면도</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -7859,7 +7856,7 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
@@ -7897,13 +7894,13 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A2- 335</t>
+          <t>A- 216</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr"/>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>입면도-배면도,좌측면도</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -7913,7 +7910,7 @@
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
@@ -7951,17 +7948,13 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>A2- 341</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>108동</t>
-        </is>
-      </c>
+          <t>A- 217</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr"/>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>지하3층 평면도</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
@@ -7971,7 +7964,7 @@
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
@@ -8009,13 +8002,13 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>A2- 342</t>
+          <t>A- 218</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr"/>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>지하2층 평면도</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -8025,7 +8018,7 @@
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
@@ -8063,13 +8056,17 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>A2- 343</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="inlineStr"/>
+          <t>A- 221</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>103동</t>
+        </is>
+      </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>지하1층 평면도</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -8079,7 +8076,7 @@
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
@@ -8117,13 +8114,13 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>A2- 344</t>
+          <t>A- 222</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr"/>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>지상1층 평면도</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -8133,7 +8130,7 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
@@ -8171,13 +8168,13 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>A2- 345</t>
+          <t>A- 223</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr"/>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>지상2층 평면도</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
@@ -8187,7 +8184,7 @@
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
@@ -8225,13 +8222,13 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>A2- 346</t>
+          <t>A- 224</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr"/>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>기준층 평면도</t>
+          <t>기준층(2~29층) 평면도</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -8241,7 +8238,7 @@
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
@@ -8279,13 +8276,13 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>A2- 347</t>
+          <t>A- 225</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr"/>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>26층 평면도</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -8295,7 +8292,7 @@
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
@@ -8333,13 +8330,13 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>A2- 348</t>
+          <t>A- 226</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr"/>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>27~28층 평면도</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
@@ -8349,7 +8346,7 @@
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
@@ -8387,13 +8384,13 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>A2- 349</t>
+          <t>A- 227</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr"/>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>29층 평면도</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
@@ -8403,7 +8400,7 @@
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
@@ -8441,13 +8438,13 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>A2- 350</t>
+          <t>A- 228</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr"/>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>30~31층 평면도</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -8457,7 +8454,7 @@
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
@@ -8495,13 +8492,17 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>A2- 351</t>
-        </is>
-      </c>
-      <c r="B150" s="1" t="inlineStr"/>
+          <t>A- 231</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>104동</t>
+        </is>
+      </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>지붕,옥탑,옥탑지붕 평면도</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -8511,7 +8512,7 @@
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
@@ -8549,13 +8550,13 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>A2- 352</t>
+          <t>A- 232</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr"/>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>입면도-정면도,우측면도</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
@@ -8565,7 +8566,7 @@
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
@@ -8603,13 +8604,13 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>A2- 353</t>
+          <t>A- 233</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr"/>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>입면도-배면도,좌측면도</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
@@ -8619,7 +8620,7 @@
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
@@ -8657,17 +8658,13 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>A2- 361</t>
-        </is>
-      </c>
-      <c r="B153" s="1" t="inlineStr">
-        <is>
-          <t>109동</t>
-        </is>
-      </c>
+          <t>A- 234</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr"/>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>지하2층 평면도</t>
+          <t>기준층(2~29층) 평면도</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
@@ -8677,7 +8674,7 @@
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
@@ -8715,13 +8712,13 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>A2- 362</t>
+          <t>A- 235</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr"/>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>지하1층 평면도</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -8731,7 +8728,7 @@
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
@@ -8769,13 +8766,13 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>A2- 363</t>
+          <t>A- 236</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr"/>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>지상1층 평면도</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
@@ -8785,7 +8782,7 @@
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
@@ -8823,13 +8820,13 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>A2- 364</t>
+          <t>A- 237</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr"/>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>지상2층 평면도</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
@@ -8839,7 +8836,7 @@
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
@@ -8877,13 +8874,13 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>A2- 365</t>
+          <t>A- 238</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr"/>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>기준층 평면도</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
@@ -8893,7 +8890,7 @@
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
@@ -8931,13 +8928,17 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>A2- 366</t>
-        </is>
-      </c>
-      <c r="B158" s="1" t="inlineStr"/>
+          <t>A- 241</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>105동</t>
+        </is>
+      </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>24층 평면도</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
@@ -8947,7 +8948,7 @@
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
@@ -8985,13 +8986,13 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>A2- 367</t>
+          <t>A- 242</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr"/>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>25~29층 평면도</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
@@ -9001,7 +9002,7 @@
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
@@ -9039,13 +9040,13 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>A2- 368</t>
+          <t>A- 243</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr"/>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>30층 평면도</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
@@ -9055,7 +9056,7 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
@@ -9093,13 +9094,13 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>A2- 369</t>
+          <t>A- 244</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr"/>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>31층 평면도</t>
+          <t>기준층(2~24층) 평면도</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
@@ -9109,7 +9110,7 @@
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
@@ -9147,13 +9148,13 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>A2- 370</t>
+          <t>A- 245</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr"/>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>지붕,옥탑,옥탑지붕 평면도</t>
+          <t>25층 평면도</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
@@ -9163,7 +9164,7 @@
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>1/300</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
@@ -9201,13 +9202,13 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>A2- 371</t>
+          <t>A- 246</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr"/>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>입면도-정면도,우측면도</t>
+          <t>26~28층 평면도</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
@@ -9217,7 +9218,7 @@
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
@@ -9255,13 +9256,13 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>A2- 372</t>
+          <t>A- 247</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr"/>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>입면도-배면도,좌측면도</t>
+          <t>29층 평면도</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
@@ -9271,7 +9272,7 @@
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>1/500</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
@@ -9309,17 +9310,13 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>A3- 361</t>
-        </is>
-      </c>
-      <c r="B165" s="1" t="inlineStr">
-        <is>
-          <t>104동</t>
-        </is>
-      </c>
+          <t>A- 248</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr"/>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-1</t>
+          <t>지붕, 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
@@ -9329,7 +9326,7 @@
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
@@ -9367,13 +9364,13 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>A3- 362</t>
+          <t>A- 249</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr"/>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-2</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
@@ -9383,7 +9380,7 @@
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
@@ -9421,13 +9418,13 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>A3- 363</t>
+          <t>A- 250</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr"/>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-3</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
@@ -9437,7 +9434,7 @@
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
@@ -9475,13 +9472,17 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>A3- 364</t>
-        </is>
-      </c>
-      <c r="B168" s="1" t="inlineStr"/>
+          <t>A- 251</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>106동</t>
+        </is>
+      </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-4</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
@@ -9491,7 +9492,7 @@
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
@@ -9529,13 +9530,13 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>A3- 365</t>
+          <t>A- 252</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr"/>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-5</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
@@ -9545,7 +9546,7 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
@@ -9583,13 +9584,13 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>A3- 366</t>
+          <t>A- 253</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr"/>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
@@ -9599,7 +9600,7 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
@@ -9637,17 +9638,13 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>A3- 371</t>
-        </is>
-      </c>
-      <c r="B171" s="1" t="inlineStr">
-        <is>
-          <t>105동</t>
-        </is>
-      </c>
+          <t>A- 254</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr"/>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-1</t>
+          <t>기준층(2~23층) 평면도</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
@@ -9657,7 +9654,7 @@
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F171" s="1" t="inlineStr">
@@ -9695,13 +9692,13 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>A3- 372</t>
+          <t>A- 255</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr"/>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-2</t>
+          <t>24층 평면도</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
@@ -9711,7 +9708,7 @@
       </c>
       <c r="E172" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F172" s="1" t="inlineStr">
@@ -9749,13 +9746,13 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>A3- 373</t>
+          <t>A- 256</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr"/>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-3</t>
+          <t>25~29층 평면도</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
@@ -9765,7 +9762,7 @@
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F173" s="1" t="inlineStr">
@@ -9803,13 +9800,13 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>A3- 374</t>
+          <t>A- 257</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr"/>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-4</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
@@ -9819,7 +9816,7 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
@@ -9857,13 +9854,13 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>A3- 375</t>
+          <t>A- 258</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr"/>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-5</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
@@ -9873,7 +9870,7 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
@@ -9911,13 +9908,13 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>A3- 376</t>
+          <t>A- 259</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr"/>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-6</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D176" s="1" t="inlineStr">
@@ -9927,7 +9924,7 @@
       </c>
       <c r="E176" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F176" s="1" t="inlineStr">
@@ -9965,13 +9962,13 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>A3- 377</t>
+          <t>A- 260</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr"/>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-7</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
@@ -9981,7 +9978,7 @@
       </c>
       <c r="E177" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F177" s="1" t="inlineStr">
@@ -10019,13 +10016,17 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>A3- 378</t>
-        </is>
-      </c>
-      <c r="B178" s="1" t="inlineStr"/>
+          <t>A- 261</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>107동</t>
+        </is>
+      </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-1</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -10035,7 +10036,7 @@
       </c>
       <c r="E178" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F178" s="1" t="inlineStr">
@@ -10073,13 +10074,13 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>A3- 379</t>
+          <t>A- 262</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr"/>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-2</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
@@ -10089,7 +10090,7 @@
       </c>
       <c r="E179" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F179" s="1" t="inlineStr">
@@ -10127,17 +10128,13 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>A3- 381</t>
-        </is>
-      </c>
-      <c r="B180" s="1" t="inlineStr">
-        <is>
-          <t>106동</t>
-        </is>
-      </c>
+          <t>A- 263</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr"/>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-1</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
@@ -10147,7 +10144,7 @@
       </c>
       <c r="E180" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F180" s="1" t="inlineStr">
@@ -10185,13 +10182,13 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>A3- 382</t>
+          <t>A- 264</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr"/>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-2</t>
+          <t>기준층(2~25층) 평면도</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
@@ -10201,7 +10198,7 @@
       </c>
       <c r="E181" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F181" s="1" t="inlineStr">
@@ -10239,13 +10236,13 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>A3- 383</t>
+          <t>A- 265</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr"/>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-3</t>
+          <t>26층 평면도</t>
         </is>
       </c>
       <c r="D182" s="1" t="inlineStr">
@@ -10255,7 +10252,7 @@
       </c>
       <c r="E182" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F182" s="1" t="inlineStr">
@@ -10293,13 +10290,13 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>A3- 384</t>
+          <t>A- 266</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr"/>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-4</t>
+          <t>27~29층 평면도</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -10309,7 +10306,7 @@
       </c>
       <c r="E183" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F183" s="1" t="inlineStr">
@@ -10347,13 +10344,13 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>A3- 385</t>
+          <t>A- 267</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr"/>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-5</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -10363,7 +10360,7 @@
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F184" s="1" t="inlineStr">
@@ -10401,13 +10398,13 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>A3- 386</t>
+          <t>A- 268</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr"/>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-6</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -10417,7 +10414,7 @@
       </c>
       <c r="E185" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F185" s="1" t="inlineStr">
@@ -10455,13 +10452,13 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>A3- 387</t>
+          <t>A- 269</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr"/>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-1</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
@@ -10471,7 +10468,7 @@
       </c>
       <c r="E186" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F186" s="1" t="inlineStr">
@@ -10509,13 +10506,13 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>A3- 388</t>
+          <t>A- 270</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr"/>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-2</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
@@ -10525,7 +10522,7 @@
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F187" s="1" t="inlineStr">
@@ -10563,17 +10560,17 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>A3- 391</t>
+          <t>A- 271</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>107동</t>
+          <t>108동</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-1</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
@@ -10583,7 +10580,7 @@
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F188" s="1" t="inlineStr">
@@ -10621,13 +10618,13 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>A3- 392</t>
+          <t>A- 272</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr"/>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-2</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
@@ -10637,7 +10634,7 @@
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F189" s="1" t="inlineStr">
@@ -10675,13 +10672,13 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>A3- 393</t>
+          <t>A- 273</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr"/>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-3</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
@@ -10691,7 +10688,7 @@
       </c>
       <c r="E190" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F190" s="1" t="inlineStr">
@@ -10729,13 +10726,13 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>A3- 394</t>
+          <t>A- 274</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr"/>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-4</t>
+          <t>기준층(2~25층) 평면도</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -10745,7 +10742,7 @@
       </c>
       <c r="E191" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F191" s="1" t="inlineStr">
@@ -10783,13 +10780,13 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>A3- 395</t>
+          <t>A- 275</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr"/>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-1</t>
+          <t>26층 평면도</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
@@ -10799,7 +10796,7 @@
       </c>
       <c r="E192" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F192" s="1" t="inlineStr">
@@ -10837,13 +10834,13 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>A3- 396</t>
+          <t>A- 276</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr"/>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-2</t>
+          <t>27~29층 평면도</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -10853,7 +10850,7 @@
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F193" s="1" t="inlineStr">
@@ -10891,13 +10888,13 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>A3- 397</t>
+          <t>A- 277</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr"/>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-1</t>
+          <t>지붕 평면도</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
@@ -10907,7 +10904,7 @@
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F194" s="1" t="inlineStr">
@@ -10945,13 +10942,13 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>A3- 398</t>
+          <t>A- 278</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr"/>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-2</t>
+          <t>옥탑 및 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
@@ -10961,7 +10958,7 @@
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
@@ -10999,13 +10996,13 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>A3- 399</t>
+          <t>A- 279</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr"/>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-3</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
@@ -11015,7 +11012,7 @@
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F196" s="1" t="inlineStr">
@@ -11053,13 +11050,13 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>A3- 400</t>
+          <t>A- 280</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr"/>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-4</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
@@ -11069,7 +11066,7 @@
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F197" s="1" t="inlineStr">
@@ -11107,13 +11104,17 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>A3- 401</t>
-        </is>
-      </c>
-      <c r="B198" s="1" t="inlineStr"/>
+          <t>A- 281</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>109동</t>
+        </is>
+      </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-5</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
@@ -11123,7 +11124,7 @@
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F198" s="1" t="inlineStr">
@@ -11161,13 +11162,13 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>A3- 402</t>
+          <t>A- 282</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr"/>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대단면도-1</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
@@ -11177,7 +11178,7 @@
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F199" s="1" t="inlineStr">
@@ -11215,13 +11216,13 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>A3- 403</t>
+          <t>A- 283</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr"/>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대단면도-2</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
@@ -11231,7 +11232,7 @@
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
@@ -11269,17 +11270,13 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>A3- 411</t>
-        </is>
-      </c>
-      <c r="B201" s="1" t="inlineStr">
-        <is>
-          <t>108동</t>
-        </is>
-      </c>
+          <t>A- 284</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="inlineStr"/>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-1</t>
+          <t>기준층(2~21층) 평면도</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
@@ -11289,7 +11286,7 @@
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
@@ -11327,13 +11324,13 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>A3- 412</t>
+          <t>A- 285</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr"/>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-2</t>
+          <t>22층 평면도</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
@@ -11343,7 +11340,7 @@
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F202" s="1" t="inlineStr">
@@ -11381,13 +11378,13 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>A3- 413</t>
+          <t>A- 286</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr"/>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-3</t>
+          <t>23층 평면도</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
@@ -11397,7 +11394,7 @@
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F203" s="1" t="inlineStr">
@@ -11435,13 +11432,13 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>A3- 414</t>
+          <t>A- 287</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr"/>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-1</t>
+          <t>24층 평면도</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
@@ -11451,7 +11448,7 @@
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F204" s="1" t="inlineStr">
@@ -11489,13 +11486,13 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>A3- 415</t>
+          <t>A- 288</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr"/>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-2</t>
+          <t>25층 평면도</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
@@ -11505,7 +11502,7 @@
       </c>
       <c r="E205" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F205" s="1" t="inlineStr">
@@ -11543,13 +11540,13 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>A3- 416</t>
+          <t>A- 289</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr"/>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-1</t>
+          <t>26~29층 평면도</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
@@ -11559,7 +11556,7 @@
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F206" s="1" t="inlineStr">
@@ -11597,13 +11594,13 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>A3- 417</t>
+          <t>A- 290</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr"/>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-2</t>
+          <t>지붕, 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
@@ -11613,7 +11610,7 @@
       </c>
       <c r="E207" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F207" s="1" t="inlineStr">
@@ -11651,13 +11648,13 @@
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>A3- 418</t>
+          <t>A- 291</t>
         </is>
       </c>
       <c r="B208" s="1" t="inlineStr"/>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-3</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
@@ -11667,7 +11664,7 @@
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F208" s="1" t="inlineStr">
@@ -11705,13 +11702,13 @@
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>A3- 419</t>
+          <t>A- 292</t>
         </is>
       </c>
       <c r="B209" s="1" t="inlineStr"/>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-4</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -11721,7 +11718,7 @@
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F209" s="1" t="inlineStr">
@@ -11759,13 +11756,17 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>A3- 420</t>
-        </is>
-      </c>
-      <c r="B210" s="1" t="inlineStr"/>
+          <t>A- 301</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>110동</t>
+        </is>
+      </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-5</t>
+          <t>() 지하2층 평면도</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -11775,7 +11776,7 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F210" s="1" t="inlineStr">
@@ -11813,13 +11814,13 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>A3- 421</t>
+          <t>A- 302</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr"/>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-6</t>
+          <t>지하1층 평면도</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
@@ -11829,7 +11830,7 @@
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F211" s="1" t="inlineStr">
@@ -11867,13 +11868,13 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>A3- 422</t>
+          <t>A- 303</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr"/>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-7</t>
+          <t>지반층 평면도</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
@@ -11883,7 +11884,7 @@
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F212" s="1" t="inlineStr">
@@ -11921,13 +11922,13 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>A3- 423</t>
+          <t>A- 304</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr"/>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대단면도-1</t>
+          <t>기준층(2~21층) 평면도</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
@@ -11937,7 +11938,7 @@
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F213" s="1" t="inlineStr">
@@ -11975,13 +11976,13 @@
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>A3- 424</t>
+          <t>A- 305</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr"/>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대단면도-2</t>
+          <t>22층 평면도</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
@@ -11991,7 +11992,7 @@
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F214" s="1" t="inlineStr">
@@ -12029,17 +12030,13 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>A3- 431</t>
-        </is>
-      </c>
-      <c r="B215" s="1" t="inlineStr">
-        <is>
-          <t>109동</t>
-        </is>
-      </c>
+          <t>A- 306</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="inlineStr"/>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-1</t>
+          <t>23층~27층 평면도</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
@@ -12049,7 +12046,7 @@
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F215" s="1" t="inlineStr">
@@ -12087,13 +12084,13 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>A3- 432</t>
+          <t>A- 307</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr"/>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-2</t>
+          <t>28층 평면도</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
@@ -12103,7 +12100,7 @@
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F216" s="1" t="inlineStr">
@@ -12141,13 +12138,13 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>A3- 433</t>
+          <t>A- 308</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr"/>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대평면도-3</t>
+          <t>지붕, 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
@@ -12157,7 +12154,7 @@
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F217" s="1" t="inlineStr">
@@ -12195,13 +12192,13 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>A3- 434</t>
+          <t>A- 309</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr"/>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-1</t>
+          <t>정면도, 우측면도</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
@@ -12211,7 +12208,7 @@
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F218" s="1" t="inlineStr">
@@ -12249,13 +12246,13 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>A3- 435</t>
+          <t>A- 310</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr"/>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>코어#1 확대단면도-2</t>
+          <t>배면도, 좌측면도</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
@@ -12265,7 +12262,7 @@
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/500</t>
         </is>
       </c>
       <c r="F219" s="1" t="inlineStr">
@@ -12303,13 +12300,13 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>A3- 436</t>
+          <t>A-400</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr"/>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-1</t>
+          <t>코아 상세도</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
@@ -12319,7 +12316,7 @@
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F220" s="1" t="inlineStr">
@@ -12357,13 +12354,17 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>A3- 437</t>
-        </is>
-      </c>
-      <c r="B221" s="1" t="inlineStr"/>
+          <t>A- 401</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t>101동</t>
+        </is>
+      </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-2</t>
+          <t>() 코어#1 지하2, 1층 평면도</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
@@ -12411,13 +12412,13 @@
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>A3- 438</t>
+          <t>A- 402</t>
         </is>
       </c>
       <c r="B222" s="1" t="inlineStr"/>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-3</t>
+          <t>코어#1 지반층, 2~29층, 지붕 평면도</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
@@ -12465,13 +12466,13 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>A3- 439</t>
+          <t>A- 403</t>
         </is>
       </c>
       <c r="B223" s="1" t="inlineStr"/>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-4</t>
+          <t>코어#1 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
@@ -12519,13 +12520,17 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>A3- 440</t>
-        </is>
-      </c>
-      <c r="B224" s="1" t="inlineStr"/>
+          <t>A- 411</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t>101동</t>
+        </is>
+      </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대평면도-5</t>
+          <t>() 코어#2 지하2, 1층 평면도</t>
         </is>
       </c>
       <c r="D224" s="1" t="inlineStr">
@@ -12573,13 +12578,13 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>A3- 441</t>
+          <t>A- 412</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr"/>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대단면도-1</t>
+          <t>코어#2 지반층, 2~26층 평면도</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
@@ -12627,13 +12632,13 @@
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>A3- 442</t>
+          <t>A- 413</t>
         </is>
       </c>
       <c r="B226" s="1" t="inlineStr"/>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>코어#2 확대단면도-2</t>
+          <t>코어#2 27층, 28~29층 평면도</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
@@ -12681,13 +12686,13 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>A3- 451</t>
+          <t>A- 414</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr"/>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>주출입구 #1 평,입,단면도</t>
+          <t>코어#2 지붕, 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
@@ -12735,13 +12740,17 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B228" s="1" t="inlineStr"/>
+          <t>A- 421</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>102동</t>
+        </is>
+      </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>부대복리시설</t>
+          <t>() 코어#1 지하2, 1층 평면도</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
@@ -12751,7 +12760,7 @@
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F228" s="1" t="inlineStr">
@@ -12789,13 +12798,13 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>A5- 501</t>
+          <t>A- 422</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr"/>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>작은도서관/주민커뮤니티 평면도</t>
+          <t>코어#1 지반층, 2~26층 평면도</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
@@ -12805,7 +12814,7 @@
       </c>
       <c r="E229" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F229" s="1" t="inlineStr">
@@ -12843,13 +12852,13 @@
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>A5- 502</t>
+          <t>A- 423</t>
         </is>
       </c>
       <c r="B230" s="1" t="inlineStr"/>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>작은도서관/주민커뮤니티 입,단면도</t>
+          <t>코어#1 지붕, 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
@@ -12859,7 +12868,7 @@
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F230" s="1" t="inlineStr">
@@ -12897,13 +12906,17 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>A5- 503</t>
-        </is>
-      </c>
-      <c r="B231" s="1" t="inlineStr"/>
+          <t>A- 431</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>105동</t>
+        </is>
+      </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>작은도서관/주민커뮤니티 창호일람표-1</t>
+          <t>() 코어 지하2, 1층 평면도</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
@@ -12951,13 +12964,13 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>A5- 504</t>
+          <t>A- 432</t>
         </is>
       </c>
       <c r="B232" s="1" t="inlineStr"/>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>작은도서관/주민커뮤니티 창호일람표-2</t>
+          <t>코어 지반층, 2~24층 평면도</t>
         </is>
       </c>
       <c r="D232" s="1" t="inlineStr">
@@ -13005,13 +13018,13 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>A5- 511</t>
+          <t>A- 433</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr"/>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>피트니스(골프연습장)/사우나 평면도</t>
+          <t>코어 25층, 26~28층 평면도</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
@@ -13021,7 +13034,7 @@
       </c>
       <c r="E233" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F233" s="1" t="inlineStr">
@@ -13059,13 +13072,13 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>A5- 512</t>
+          <t>A- 434</t>
         </is>
       </c>
       <c r="B234" s="1" t="inlineStr"/>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t>피트니스(골프연습장)/사우나 입,단면도</t>
+          <t>코어 29층, 지붕 평면도</t>
         </is>
       </c>
       <c r="D234" s="1" t="inlineStr">
@@ -13075,7 +13088,7 @@
       </c>
       <c r="E234" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F234" s="1" t="inlineStr">
@@ -13113,13 +13126,13 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>A5- 513</t>
+          <t>A- 435</t>
         </is>
       </c>
       <c r="B235" s="1" t="inlineStr"/>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t>피트니스(골프연습장)/사우나 창호일람표</t>
+          <t>코어 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
@@ -13167,13 +13180,17 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>A5- 521</t>
-        </is>
-      </c>
-      <c r="B236" s="1" t="inlineStr"/>
+          <t>A- 441</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>106동</t>
+        </is>
+      </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t>경로당,다함께돌봄센터,관리사무실 평면도</t>
+          <t>() 코어#1 지하2, 1층 평면도</t>
         </is>
       </c>
       <c r="D236" s="1" t="inlineStr">
@@ -13183,7 +13200,7 @@
       </c>
       <c r="E236" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F236" s="1" t="inlineStr">
@@ -13221,13 +13238,13 @@
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>A5- 522</t>
+          <t>A- 442</t>
         </is>
       </c>
       <c r="B237" s="1" t="inlineStr"/>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t>경로당,다함께돌봄센터,관리사무실 입,단면도</t>
+          <t>코어#1 지반층, 2~23층 평면도</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
@@ -13237,7 +13254,7 @@
       </c>
       <c r="E237" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F237" s="1" t="inlineStr">
@@ -13275,13 +13292,13 @@
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>A5- 523</t>
+          <t>A- 443</t>
         </is>
       </c>
       <c r="B238" s="1" t="inlineStr"/>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t>경로당,다함께돌봄센터,관리사무실 창호일람표</t>
+          <t>코어#1 24층, 25~29층 평면도</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
@@ -13329,13 +13346,13 @@
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>A5- 531</t>
+          <t>A- 444</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr"/>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>어린이집 평,입,단면도</t>
+          <t>코어#1 지붕, 옥탑, 옥탑지붕 평면도</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
@@ -13345,7 +13362,7 @@
       </c>
       <c r="E239" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F239" s="1" t="inlineStr">
@@ -13383,13 +13400,13 @@
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>A5- 532</t>
+          <t>A-500</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr"/>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>어린이집 창호일람표</t>
+          <t>지하주차장 관련도면</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
@@ -13399,7 +13416,7 @@
       </c>
       <c r="E240" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>X</t>
         </is>
       </c>
       <c r="F240" s="1" t="inlineStr">
@@ -13437,13 +13454,13 @@
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>A5- 541</t>
+          <t>A- 501</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr"/>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t>근린생활시설-1 평,입,단면도</t>
+          <t>지하2층 주차장 평면도</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
@@ -13453,7 +13470,7 @@
       </c>
       <c r="E241" s="1" t="inlineStr">
         <is>
-          <t>1/200</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F241" s="1" t="inlineStr">
@@ -13491,13 +13508,13 @@
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>A5- 542</t>
+          <t>A- 502</t>
         </is>
       </c>
       <c r="B242" s="1" t="inlineStr"/>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>근린생활시설-1 창호일람표</t>
+          <t>지하1층 주차장 평면도</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
@@ -13507,7 +13524,7 @@
       </c>
       <c r="E242" s="1" t="inlineStr">
         <is>
-          <t>1/100</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="F242" s="1" t="inlineStr">
@@ -13545,13 +13562,13 @@
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>A5- 551</t>
+          <t>A- 511</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr"/>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>문주 및 경비실 평면도</t>
+          <t>저수조/펌프실,전기/발전기실,펌프실,우수조 평면도</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
@@ -13561,7 +13578,7 @@
       </c>
       <c r="E243" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F243" s="1" t="inlineStr">
@@ -13599,13 +13616,13 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>A5- 552</t>
+          <t>A- 512</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr"/>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>문주 및 경비실 입면도</t>
+          <t>저수조/펌프실,전기/발전기실,펌프실,우수조 단면도</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
@@ -13615,7 +13632,7 @@
       </c>
       <c r="E244" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F244" s="1" t="inlineStr">
@@ -13653,13 +13670,13 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>A5- 553</t>
+          <t>A- 521</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr"/>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t>문주 및 경비실 단면도 및 창호일람표</t>
+          <t>지하주차장 창호일람표</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
@@ -13669,7 +13686,7 @@
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t>1/120</t>
+          <t>1/100</t>
         </is>
       </c>
       <c r="F245" s="1" t="inlineStr">
@@ -13707,13 +13724,13 @@
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>A5- 561</t>
+          <t>A- 531</t>
         </is>
       </c>
       <c r="B246" s="1" t="inlineStr"/>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>쓰레기 분리수거함 위치 및 상세도</t>
+          <t>(램프#1) 지하1층,1층 평,단면도</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
@@ -13723,7 +13740,7 @@
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>1/200</t>
         </is>
       </c>
       <c r="F246" s="1" t="inlineStr">
@@ -13753,6 +13770,1522 @@
         </is>
       </c>
       <c r="L246" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>A- 532</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr"/>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>(램프#2) 지하1층,1층 평,단면도</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F247" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G247" s="1" t="inlineStr"/>
+      <c r="H247" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I247" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K247" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L247" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>A- 533</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr"/>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>(램프#3) 지하2,지하1층 평,단면도</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G248" s="1" t="inlineStr"/>
+      <c r="H248" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I248" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K248" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L248" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>A-600</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="inlineStr"/>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>주민공동/부대복리시설 관련도면</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G249" s="1" t="inlineStr"/>
+      <c r="H249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K249" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L249" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>A- 601</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>주민운동</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>시설/지역공유플랫폼 평면도</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="F250" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G250" s="1" t="inlineStr"/>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I250" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K250" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L250" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>A- 602</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="inlineStr"/>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>시설/지역공유플랫폼 입단면도</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>1/300</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G251" s="1" t="inlineStr"/>
+      <c r="H251" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I251" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K251" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L251" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>A- 603</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="inlineStr"/>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>시설/지역공유플랫폼 창호일람표-1</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F252" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G252" s="1" t="inlineStr"/>
+      <c r="H252" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I252" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J252" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K252" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L252" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>A- 604</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="inlineStr"/>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>시설/지역공유플랫폼 창호일람표-2</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F253" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G253" s="1" t="inlineStr"/>
+      <c r="H253" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I253" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J253" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K253" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L253" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>A- 611</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="inlineStr"/>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>관리사무소 평,입,단면도</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F254" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G254" s="1" t="inlineStr"/>
+      <c r="H254" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I254" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J254" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K254" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L254" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>A- 612</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr"/>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>관리사무소 창호일람표</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E255" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G255" s="1" t="inlineStr"/>
+      <c r="H255" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I255" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K255" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L255" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>A- 621</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr"/>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>작은도서관 평,입,단면도</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F256" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G256" s="1" t="inlineStr"/>
+      <c r="H256" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I256" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J256" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K256" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L256" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>A- 622</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="inlineStr"/>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>작은도서관 창호일람표</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F257" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G257" s="1" t="inlineStr"/>
+      <c r="H257" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I257" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J257" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K257" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L257" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>A- 631</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="inlineStr"/>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>경로당/돌봄센터 평,입,단면도</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G258" s="1" t="inlineStr"/>
+      <c r="H258" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I258" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J258" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K258" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L258" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>A- 632</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr"/>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>경로당/돌봄센터 창호일람표</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F259" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G259" s="1" t="inlineStr"/>
+      <c r="H259" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I259" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J259" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K259" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L259" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>A- 641</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="inlineStr"/>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>어린이집 평면도</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F260" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G260" s="1" t="inlineStr"/>
+      <c r="H260" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I260" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J260" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K260" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L260" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>A- 642</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="inlineStr"/>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>어린이집 입,단면도</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G261" s="1" t="inlineStr"/>
+      <c r="H261" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I261" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J261" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K261" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L261" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>A- 643</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="inlineStr"/>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>어린이집 창호일람표</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F262" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G262" s="1" t="inlineStr"/>
+      <c r="H262" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I262" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J262" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K262" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L262" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>A- 651</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="inlineStr"/>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>맘스테이션 평,입,단면도</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F263" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G263" s="1" t="inlineStr"/>
+      <c r="H263" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I263" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J263" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K263" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L263" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>A- 652</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="inlineStr"/>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>맘스테이션 창호일람표</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F264" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G264" s="1" t="inlineStr"/>
+      <c r="H264" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I264" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J264" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K264" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L264" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>A- 653</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr"/>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>경비실 평,입,단면도</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E265" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F265" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G265" s="1" t="inlineStr"/>
+      <c r="H265" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I265" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J265" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K265" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L265" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>A- 654</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="inlineStr"/>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>경비실 창호일람표</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E266" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F266" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G266" s="1" t="inlineStr"/>
+      <c r="H266" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I266" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J266" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K266" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L266" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>A- 655</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr"/>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>근로자휴게실 평,입,단면도</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E267" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F267" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G267" s="1" t="inlineStr"/>
+      <c r="H267" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I267" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J267" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K267" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L267" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>A- 656</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="inlineStr"/>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>근로자휴게실 창호일람표</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E268" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F268" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G268" s="1" t="inlineStr"/>
+      <c r="H268" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I268" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J268" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K268" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L268" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>A- 661</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="inlineStr"/>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>(근린생활시설#1) 평면도</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F269" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G269" s="1" t="inlineStr"/>
+      <c r="H269" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I269" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J269" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K269" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L269" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>A- 662</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr"/>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>입,단면도</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F270" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G270" s="1" t="inlineStr"/>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I270" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J270" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K270" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L270" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>A- 663</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="inlineStr"/>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>창호일람표</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E271" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F271" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G271" s="1" t="inlineStr"/>
+      <c r="H271" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I271" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J271" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K271" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L271" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>A- 664</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="inlineStr"/>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>(근린생활시설#2) 평면도</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E272" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F272" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G272" s="1" t="inlineStr"/>
+      <c r="H272" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I272" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J272" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K272" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L272" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>A- 665</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="inlineStr"/>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>입,단면도</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="inlineStr">
+        <is>
+          <t>1/200</t>
+        </is>
+      </c>
+      <c r="F273" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G273" s="1" t="inlineStr"/>
+      <c r="H273" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I273" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J273" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K273" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L273" s="1" t="inlineStr">
+        <is>
+          <t>DWG 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>A- 666</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr"/>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>창호일람표</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t>1/100</t>
+        </is>
+      </c>
+      <c r="F274" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G274" s="1" t="inlineStr"/>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I274" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J274" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K274" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L274" s="1" t="inlineStr">
         <is>
           <t>DWG 누락</t>
         </is>

--- a/도면검토리포트_최종.xlsx
+++ b/도면검토리포트_최종.xlsx
@@ -931,12 +931,12 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>1/1000</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="J157" s="1" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="J158" s="1" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="J159" s="1" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="J160" s="1" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="I161" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="J161" s="1" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>1/2000</t>
         </is>
       </c>
       <c r="J162" s="1" t="inlineStr">
@@ -9254,7 +9254,7 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>A2 - 000</t>
+          <t>A2--000</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>A2 - 010</t>
+          <t>A2 010</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>A2 - 111</t>
+          <t>A2--111</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
@@ -9424,7 +9424,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>A2 - 112</t>
+          <t>A2-112</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr"/>
@@ -9478,7 +9478,7 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>A2 - 113</t>
+          <t>A2-113</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
@@ -9536,7 +9536,7 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>A2 - 114</t>
+          <t>A2-114</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>A2 - 115</t>
+          <t>A2-115</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
@@ -9648,7 +9648,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>A2 - 116</t>
+          <t>A2 116</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr"/>
@@ -9702,7 +9702,7 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>A2 - 121</t>
+          <t>A2--121</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
@@ -9760,7 +9760,7 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>A2 - 122</t>
+          <t>A2-122</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr"/>
@@ -9814,7 +9814,7 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>A2 - 123</t>
+          <t>A2-123</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr"/>
@@ -9868,7 +9868,7 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>A2 - 124</t>
+          <t>A2-124</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr"/>
@@ -9922,7 +9922,7 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>A2 - 125</t>
+          <t>A2-125</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
@@ -9980,7 +9980,7 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>A2 - 126</t>
+          <t>A2-126</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr"/>
@@ -10034,7 +10034,7 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>A2 - 127</t>
+          <t>A2-127</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr"/>
@@ -10088,7 +10088,7 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>A2 - 128</t>
+          <t>A2-128</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>A2 - 129</t>
+          <t>A2-129</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
@@ -10200,7 +10200,7 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>A2 - 130</t>
+          <t>A2-130</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr"/>
@@ -10254,7 +10254,7 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>A2 - 131</t>
+          <t>A2-131</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr"/>
@@ -10308,7 +10308,7 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>A2 - 132</t>
+          <t>A2 132</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr"/>
@@ -10362,7 +10362,7 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>A2 - 141</t>
+          <t>A2--141</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
@@ -10420,7 +10420,7 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>A2 - 142</t>
+          <t>A2-142</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr"/>
@@ -10474,7 +10474,7 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>A2 - 143</t>
+          <t>A2-143</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr"/>
@@ -10528,7 +10528,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>A2 - 144</t>
+          <t>A2-144</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>A2 - 145</t>
+          <t>A2-145</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr"/>
@@ -10640,7 +10640,7 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>A2 - 146</t>
+          <t>A2-146</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>A2 - 147</t>
+          <t>A2-147</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
@@ -10752,7 +10752,7 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>A2 - 148</t>
+          <t>A2-148</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>A2 - 149</t>
+          <t>A2 149</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr"/>
@@ -10860,7 +10860,7 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>A2 - 151</t>
+          <t>A2--151</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
@@ -10918,7 +10918,7 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>A2 - 152</t>
+          <t>A2-152</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr"/>
@@ -10972,7 +10972,7 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>A2 - 153</t>
+          <t>A2-153</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr"/>
@@ -11026,7 +11026,7 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>A2 - 154</t>
+          <t>A2-154</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
@@ -11084,7 +11084,7 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>A2 - 155</t>
+          <t>A2-155</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr"/>
@@ -11138,7 +11138,7 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>A2 - 156</t>
+          <t>A2-156</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr"/>
@@ -11192,7 +11192,7 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>A2 - 157</t>
+          <t>A2-157</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
@@ -11250,7 +11250,7 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>A2 - 158</t>
+          <t>A2-158</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr"/>
@@ -11304,7 +11304,7 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>A2 - 159</t>
+          <t>A2 159</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>A2 - 201</t>
+          <t>A2--201</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>A2 - 202</t>
+          <t>A2-202</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr"/>
@@ -11470,7 +11470,7 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>A2 - 203</t>
+          <t>A2-203</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr"/>
@@ -11524,7 +11524,7 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>A2 - 204</t>
+          <t>A2-204</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr"/>
@@ -11578,7 +11578,7 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>A2 - 205</t>
+          <t>A2-205</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr">
@@ -11636,7 +11636,7 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>A2 - 206</t>
+          <t>A2-206</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr"/>
@@ -11690,7 +11690,7 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>A2 - 207</t>
+          <t>A2-207</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr"/>
@@ -11744,7 +11744,7 @@
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>A2 - 208</t>
+          <t>A2-208</t>
         </is>
       </c>
       <c r="B208" s="1" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>A2 - 209</t>
+          <t>A2-209</t>
         </is>
       </c>
       <c r="B209" s="1" t="inlineStr">
@@ -11856,7 +11856,7 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>A2 - 210</t>
+          <t>A2-210</t>
         </is>
       </c>
       <c r="B210" s="1" t="inlineStr"/>
@@ -11910,7 +11910,7 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>A2 - 211</t>
+          <t>A2-211</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr"/>
@@ -11964,7 +11964,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>A2 - 212</t>
+          <t>A2-212</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>A2 - 213</t>
+          <t>A2-213</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr"/>
@@ -12072,7 +12072,7 @@
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>A2 - 214</t>
+          <t>A2-214</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr"/>
@@ -12126,7 +12126,7 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>A2 - 215</t>
+          <t>A2-215</t>
         </is>
       </c>
       <c r="B215" s="1" t="inlineStr"/>
@@ -12180,7 +12180,7 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>A2 - 216</t>
+          <t>A2 216</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr"/>
@@ -12234,7 +12234,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>A2 - 301</t>
+          <t>A2--301</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
@@ -12292,7 +12292,7 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>A2 - 302</t>
+          <t>A2-302</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr"/>
@@ -12346,7 +12346,7 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>A2 - 303</t>
+          <t>A2-303</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
@@ -12404,7 +12404,7 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>A2 - 304</t>
+          <t>A2-304</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr"/>
@@ -12458,7 +12458,7 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>A2 - 305</t>
+          <t>A2-305</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
@@ -12516,7 +12516,7 @@
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>A2 - 306</t>
+          <t>A2 306</t>
         </is>
       </c>
       <c r="B222" s="1" t="inlineStr"/>
@@ -12570,7 +12570,7 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>A2 - 401</t>
+          <t>A2--401</t>
         </is>
       </c>
       <c r="B223" s="1" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>A2 - 402</t>
+          <t>A2-402</t>
         </is>
       </c>
       <c r="B224" s="1" t="inlineStr">
@@ -12686,7 +12686,7 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>A2 - 403</t>
+          <t>A2-403</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>A2 - 404</t>
+          <t>A2-404</t>
         </is>
       </c>
       <c r="B226" s="1" t="inlineStr"/>
@@ -12798,7 +12798,7 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>A2 - 405</t>
+          <t>A2 405</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr"/>
@@ -12852,7 +12852,7 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>A2 - 501</t>
+          <t>A2--501</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
@@ -12910,7 +12910,7 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>A2 - 502</t>
+          <t>A2 502</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr"/>
@@ -12964,7 +12964,7 @@
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>A2 - 601</t>
+          <t>A2--601</t>
         </is>
       </c>
       <c r="B230" s="1" t="inlineStr"/>
@@ -13018,7 +13018,7 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>A2 - 602</t>
+          <t>A2-602</t>
         </is>
       </c>
       <c r="B231" s="1" t="inlineStr"/>
@@ -13072,7 +13072,7 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>A2 - 603</t>
+          <t>A2-603</t>
         </is>
       </c>
       <c r="B232" s="1" t="inlineStr"/>
@@ -13126,7 +13126,7 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>A2 - 604</t>
+          <t>A2 604</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr"/>
@@ -13180,7 +13180,7 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>A2 - 701</t>
+          <t>A2--701</t>
         </is>
       </c>
       <c r="B234" s="1" t="inlineStr">
@@ -13238,7 +13238,7 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>A2 - 702</t>
+          <t>A2-702</t>
         </is>
       </c>
       <c r="B235" s="1" t="inlineStr"/>
@@ -13292,7 +13292,7 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>A2 - 703</t>
+          <t>A2-703</t>
         </is>
       </c>
       <c r="B236" s="1" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>A2 - 704</t>
+          <t>A2-704</t>
         </is>
       </c>
       <c r="B237" s="1" t="inlineStr">
@@ -13404,7 +13404,7 @@
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>A2 - 705</t>
+          <t>A2-705</t>
         </is>
       </c>
       <c r="B238" s="1" t="inlineStr"/>
@@ -13458,7 +13458,7 @@
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>A2 - 706</t>
+          <t>A2 706</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr"/>
@@ -13512,7 +13512,7 @@
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>A2 - 801</t>
+          <t>A2--801</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>A2 - 802</t>
+          <t>A2-802</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr"/>
@@ -13620,7 +13620,7 @@
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>A2 - 803</t>
+          <t>A2-803</t>
         </is>
       </c>
       <c r="B242" s="1" t="inlineStr"/>
@@ -13674,7 +13674,7 @@
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>A2 - 804</t>
+          <t>A2-804</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr"/>
@@ -13728,7 +13728,7 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>A2 - 805</t>
+          <t>A2-805</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr"/>
@@ -13782,7 +13782,7 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>A2 - 806</t>
+          <t>A2-806</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr"/>
@@ -13836,7 +13836,7 @@
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>A2 - 807</t>
+          <t>A2-807</t>
         </is>
       </c>
       <c r="B246" s="1" t="inlineStr"/>
@@ -13890,7 +13890,7 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>A2 - 808</t>
+          <t>A2-808</t>
         </is>
       </c>
       <c r="B247" s="1" t="inlineStr"/>
@@ -13944,7 +13944,7 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>A2 - 809</t>
+          <t>A2-809</t>
         </is>
       </c>
       <c r="B248" s="1" t="inlineStr"/>
@@ -13998,7 +13998,7 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>A2 - 810</t>
+          <t>A2 810</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>A4 - 000</t>
+          <t>A4--000</t>
         </is>
       </c>
       <c r="B250" s="1" t="inlineStr"/>
@@ -14106,7 +14106,7 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>A4 - 010</t>
+          <t>A4 010</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
@@ -14164,7 +14164,7 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>A4 - 111</t>
+          <t>A4--111</t>
         </is>
       </c>
       <c r="B252" s="1" t="inlineStr"/>
@@ -14218,7 +14218,7 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>A4 - 112</t>
+          <t>A4 112</t>
         </is>
       </c>
       <c r="B253" s="1" t="inlineStr"/>
@@ -14272,7 +14272,7 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>A4 - 121</t>
+          <t>A4--121</t>
         </is>
       </c>
       <c r="B254" s="1" t="inlineStr"/>
@@ -14326,7 +14326,7 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>A4 - 122</t>
+          <t>A4-122</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr"/>
@@ -14380,7 +14380,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>A4 - 123</t>
+          <t>A4-123</t>
         </is>
       </c>
       <c r="B256" s="1" t="inlineStr"/>
@@ -14434,7 +14434,7 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>A4 - 124</t>
+          <t>A4 124</t>
         </is>
       </c>
       <c r="B257" s="1" t="inlineStr"/>
@@ -14488,7 +14488,7 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>A4 - 131</t>
+          <t>A4--131</t>
         </is>
       </c>
       <c r="B258" s="1" t="inlineStr"/>
@@ -14542,7 +14542,7 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>A4 - 132</t>
+          <t>A4-132</t>
         </is>
       </c>
       <c r="B259" s="1" t="inlineStr"/>
@@ -14596,7 +14596,7 @@
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>A4 - 133</t>
+          <t>A4 133</t>
         </is>
       </c>
       <c r="B260" s="1" t="inlineStr"/>
@@ -14650,7 +14650,7 @@
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>A4 - 141</t>
+          <t>A4--141</t>
         </is>
       </c>
       <c r="B261" s="1" t="inlineStr"/>
@@ -14704,7 +14704,7 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>A4 - 142</t>
+          <t>A4-142</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr"/>
@@ -14758,7 +14758,7 @@
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>A4 - 143</t>
+          <t>A4 143</t>
         </is>
       </c>
       <c r="B263" s="1" t="inlineStr"/>
@@ -14812,7 +14812,7 @@
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>A4 - 201</t>
+          <t>A4 201</t>
         </is>
       </c>
       <c r="B264" s="1" t="inlineStr"/>
@@ -14866,7 +14866,7 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>A4 - 202</t>
+          <t>A4---202</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr"/>
@@ -14920,7 +14920,7 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>A4 - 203</t>
+          <t>A4-203</t>
         </is>
       </c>
       <c r="B266" s="1" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>A4 - 204</t>
+          <t>A4 204</t>
         </is>
       </c>
       <c r="B267" s="1" t="inlineStr"/>
@@ -15028,7 +15028,7 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>A4 - 301</t>
+          <t>A4--301</t>
         </is>
       </c>
       <c r="B268" s="1" t="inlineStr"/>
@@ -15082,7 +15082,7 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>A4 - 302</t>
+          <t>A4 302</t>
         </is>
       </c>
       <c r="B269" s="1" t="inlineStr"/>
@@ -15136,7 +15136,7 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>A4 - 401</t>
+          <t>A4--401</t>
         </is>
       </c>
       <c r="B270" s="1" t="inlineStr"/>
@@ -15190,7 +15190,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>A4 - 402</t>
+          <t>A4 402</t>
         </is>
       </c>
       <c r="B271" s="1" t="inlineStr"/>
@@ -15244,7 +15244,7 @@
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>A4 - 501</t>
+          <t>A4--501</t>
         </is>
       </c>
       <c r="B272" s="1" t="inlineStr"/>
@@ -15298,7 +15298,7 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>A4 - 502</t>
+          <t>A4-502</t>
         </is>
       </c>
       <c r="B273" s="1" t="inlineStr"/>
@@ -15352,7 +15352,7 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>A4 - 503</t>
+          <t>A4-503</t>
         </is>
       </c>
       <c r="B274" s="1" t="inlineStr"/>
@@ -15406,7 +15406,7 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>A4 - 504</t>
+          <t>A4-504</t>
         </is>
       </c>
       <c r="B275" s="1" t="inlineStr"/>
@@ -15460,7 +15460,7 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>A4 - 505</t>
+          <t>A4 505</t>
         </is>
       </c>
       <c r="B276" s="1" t="inlineStr"/>
@@ -15514,7 +15514,7 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>A4 - 601</t>
+          <t>A4-601</t>
         </is>
       </c>
       <c r="B277" s="1" t="inlineStr"/>
@@ -15568,7 +15568,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>A4 - 701</t>
+          <t>A4--701</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr"/>
@@ -15622,7 +15622,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>A4 - 702</t>
+          <t>A4-702</t>
         </is>
       </c>
       <c r="B279" s="1" t="inlineStr"/>
@@ -15676,7 +15676,7 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>A4 - 703</t>
+          <t>A4-703</t>
         </is>
       </c>
       <c r="B280" s="1" t="inlineStr"/>
@@ -15730,7 +15730,7 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>A4 - 704</t>
+          <t>A4 704</t>
         </is>
       </c>
       <c r="B281" s="1" t="inlineStr"/>
@@ -15784,7 +15784,7 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>A5 - 000</t>
+          <t>A5--000</t>
         </is>
       </c>
       <c r="B282" s="1" t="inlineStr"/>
@@ -15838,7 +15838,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>A5 - 010</t>
+          <t>A5 010</t>
         </is>
       </c>
       <c r="B283" s="1" t="inlineStr"/>
@@ -15892,7 +15892,7 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>A5 - 111</t>
+          <t>A5-111</t>
         </is>
       </c>
       <c r="B284" s="1" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>A5 - 121</t>
+          <t>A5--121</t>
         </is>
       </c>
       <c r="B285" s="1" t="inlineStr"/>
@@ -16004,7 +16004,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>A5 - 122</t>
+          <t>A5 122</t>
         </is>
       </c>
       <c r="B286" s="1" t="inlineStr"/>
@@ -16058,7 +16058,7 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>A5 - 131</t>
+          <t>A5--131</t>
         </is>
       </c>
       <c r="B287" s="1" t="inlineStr"/>
@@ -16112,7 +16112,7 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>A5 - 132</t>
+          <t>A5 132</t>
         </is>
       </c>
       <c r="B288" s="1" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>A5 - 141</t>
+          <t>A5-141</t>
         </is>
       </c>
       <c r="B289" s="1" t="inlineStr"/>
@@ -16220,7 +16220,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>A5 - 201</t>
+          <t>A5--201</t>
         </is>
       </c>
       <c r="B290" s="1" t="inlineStr"/>
@@ -16274,7 +16274,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>A5 - 202</t>
+          <t>A5 202</t>
         </is>
       </c>
       <c r="B291" s="1" t="inlineStr"/>
@@ -16328,7 +16328,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>A5 - 301</t>
+          <t>A5--301</t>
         </is>
       </c>
       <c r="B292" s="1" t="inlineStr"/>
@@ -16382,7 +16382,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>A5 - 302</t>
+          <t>A5 302</t>
         </is>
       </c>
       <c r="B293" s="1" t="inlineStr"/>
@@ -16436,7 +16436,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>A5 - 401</t>
+          <t>A5-401</t>
         </is>
       </c>
       <c r="B294" s="1" t="inlineStr"/>
@@ -16490,7 +16490,7 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>A5 - 501</t>
+          <t>A5-501</t>
         </is>
       </c>
       <c r="B295" s="1" t="inlineStr"/>
@@ -16544,7 +16544,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>A5 - 601</t>
+          <t>A5--601</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>A5 - 602</t>
+          <t>A5 602</t>
         </is>
       </c>
       <c r="B297" s="1" t="inlineStr"/>
@@ -16652,7 +16652,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>A6 - 000</t>
+          <t>A6--000</t>
         </is>
       </c>
       <c r="B298" s="1" t="inlineStr"/>
@@ -16706,7 +16706,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>A6 - 010</t>
+          <t>A6 010</t>
         </is>
       </c>
       <c r="B299" s="1" t="inlineStr"/>
@@ -16760,7 +16760,7 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>A6 - 111</t>
+          <t>A6--111</t>
         </is>
       </c>
       <c r="B300" s="1" t="inlineStr"/>
@@ -16814,7 +16814,7 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>A6 - 121</t>
+          <t>A6 121</t>
         </is>
       </c>
       <c r="B301" s="1" t="inlineStr"/>
@@ -16868,7 +16868,7 @@
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>A6 - 201</t>
+          <t>A6-201</t>
         </is>
       </c>
       <c r="B302" s="1" t="inlineStr"/>
@@ -16922,7 +16922,7 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>A6 - 301</t>
+          <t>A6--301</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>A6 - 302</t>
+          <t>A6 302</t>
         </is>
       </c>
       <c r="B304" s="1" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>A6 - 401</t>
+          <t>A6-401</t>
         </is>
       </c>
       <c r="B305" s="1" t="inlineStr"/>
@@ -17084,7 +17084,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>A6 - 501</t>
+          <t>A6-501</t>
         </is>
       </c>
       <c r="B306" s="1" t="inlineStr"/>
@@ -17138,7 +17138,7 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>A7 - 101</t>
+          <t>A7--101</t>
         </is>
       </c>
       <c r="B307" s="1" t="inlineStr"/>
@@ -17192,7 +17192,7 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>A7 - 102</t>
+          <t>A7 102</t>
         </is>
       </c>
       <c r="B308" s="1" t="inlineStr"/>

--- a/도면검토리포트_최종.xlsx
+++ b/도면검토리포트_최종.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A0--001</t>
+          <t>A0-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,19 +496,19 @@
           <t>목록표-1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A0 001</t>
+          <t>A0-001</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,14 +516,14 @@
           <t>목록표-1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>NONE</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -548,19 +548,19 @@
           <t>목록표-2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A0 002</t>
+          <t>A0-002</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -568,14 +568,14 @@
           <t>목록표-2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>NONE</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -600,19 +600,19 @@
           <t>목록표-3</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A0 003</t>
+          <t>A0-003</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -620,14 +620,14 @@
           <t>목록표-3</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>NONE</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -652,19 +652,19 @@
           <t>목록표-4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A0 004</t>
+          <t>A0-004</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -672,14 +672,14 @@
           <t>목록표-4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>NONE</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>A0--005</t>
+          <t>A0-005</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr"/>
@@ -912,7 +912,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>A0--010</t>
+          <t>A0-010</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr"/>
@@ -1398,7 +1398,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A0--201</t>
+          <t>A0-201</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1411,14 +1411,14 @@
           <t>1/1000</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>1/2000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A0 201</t>
+          <t>A0-201</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>1/2000</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1463,14 +1463,14 @@
           <t>1/1000</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>1/2000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A0 202</t>
+          <t>A0-202</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>1/2000</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1515,14 +1515,14 @@
           <t>1/1000</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>1/2000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A0 203</t>
+          <t>A0-203</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>1/2000</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1567,14 +1567,14 @@
           <t>1/1000</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>1/2000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A0 204</t>
+          <t>A0-204</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>1/2000</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1619,14 +1619,14 @@
           <t>1/1000</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>1/2000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A0 205</t>
+          <t>A0-205</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>1/2000</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1671,14 +1671,14 @@
           <t>1/1000</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>1/2000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A0 206</t>
+          <t>A0-206</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>1/2000</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>A0--301</t>
+          <t>A0-301</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>A0--401</t>
+          <t>A0-401</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>A0--501</t>
+          <t>A0-501</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr"/>
@@ -2578,7 +2578,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>A0--606</t>
+          <t>A0-606</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>A0--701</t>
+          <t>A0-701</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>A0---706</t>
+          <t>A0-706</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
@@ -3416,7 +3416,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>A0--721</t>
+          <t>A0-721</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
@@ -4014,7 +4014,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>A0--741</t>
+          <t>A0-741</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
@@ -4882,7 +4882,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>A0--757</t>
+          <t>A0-757</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr"/>
@@ -5908,7 +5908,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>A0--781</t>
+          <t>A0-781</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
@@ -6074,7 +6074,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>A0--791</t>
+          <t>A0-791</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
@@ -6294,7 +6294,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>A0--801</t>
+          <t>A0-801</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>A0--811</t>
+          <t>A0-811</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>A0--901</t>
+          <t>A0-901</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr"/>
@@ -7378,7 +7378,7 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>A0--908</t>
+          <t>A0-908</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>A0--911</t>
+          <t>A0-911</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
@@ -7768,7 +7768,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A0---916</t>
+          <t>A0-916</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr"/>
@@ -7880,7 +7880,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A0 918</t>
+          <t>A0-918</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A0-919</t>
+          <t>A0 919</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
@@ -7992,7 +7992,7 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>A0--920</t>
+          <t>A0-920</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
@@ -8050,7 +8050,7 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>A0 921</t>
+          <t>A0-921</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>A0--931</t>
+          <t>A0-931</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr"/>
@@ -8212,7 +8212,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>A0--941</t>
+          <t>A0-941</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr"/>
@@ -8374,7 +8374,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>A0 944</t>
+          <t>A0-944</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr"/>
@@ -8482,7 +8482,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>A0-946</t>
+          <t>A0 946</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>A1--000</t>
+          <t>A1-000</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr"/>
@@ -8648,7 +8648,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>A1--111</t>
+          <t>A1-111</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr"/>
@@ -8756,7 +8756,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>A1--121</t>
+          <t>A1-121</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>A1--131</t>
+          <t>A1-131</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr"/>
@@ -9080,7 +9080,7 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>A1--141</t>
+          <t>A1-141</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr"/>
@@ -9242,7 +9242,7 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>A1--201</t>
+          <t>A1-201</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr"/>
@@ -9404,7 +9404,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>A1--301</t>
+          <t>A1-301</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr"/>
@@ -9566,7 +9566,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>A1--501</t>
+          <t>A1-501</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>A1--601</t>
+          <t>A1-601</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr"/>
@@ -10160,7 +10160,7 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>A1--621</t>
+          <t>A1-621</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr"/>
@@ -10484,7 +10484,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>A1--631</t>
+          <t>A1-631</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr"/>
@@ -10592,7 +10592,7 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>A1--701</t>
+          <t>A1-701</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr"/>
@@ -10754,7 +10754,7 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>A2--000</t>
+          <t>A2-000</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr"/>
@@ -10866,7 +10866,7 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>A2--111</t>
+          <t>A2-111</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
@@ -11202,7 +11202,7 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>A2--121</t>
+          <t>A2-121</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
@@ -11862,7 +11862,7 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>A2--141</t>
+          <t>A2-141</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr">
@@ -12360,7 +12360,7 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>A2--151</t>
+          <t>A2-151</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
@@ -12858,7 +12858,7 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>A2--201</t>
+          <t>A2-201</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>A2--301</t>
+          <t>A2-301</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr">
@@ -14070,7 +14070,7 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>A2--401</t>
+          <t>A2-401</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
@@ -14352,7 +14352,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>A2--501</t>
+          <t>A2-501</t>
         </is>
       </c>
       <c r="B256" s="1" t="inlineStr">
@@ -14464,7 +14464,7 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>A2--601</t>
+          <t>A2-601</t>
         </is>
       </c>
       <c r="B258" s="1" t="inlineStr"/>
@@ -14680,7 +14680,7 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>A2--701</t>
+          <t>A2-701</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr">
@@ -15012,7 +15012,7 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>A2--801</t>
+          <t>A2-801</t>
         </is>
       </c>
       <c r="B268" s="1" t="inlineStr"/>
@@ -15552,7 +15552,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>A3--000</t>
+          <t>A3-000</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>A3--121</t>
+          <t>A3-121</t>
         </is>
       </c>
       <c r="B281" s="1" t="inlineStr"/>
@@ -15826,7 +15826,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>A3--131</t>
+          <t>A3-131</t>
         </is>
       </c>
       <c r="B283" s="1" t="inlineStr"/>
@@ -16042,7 +16042,7 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>A3--202</t>
+          <t>A3-202</t>
         </is>
       </c>
       <c r="B287" s="1" t="inlineStr"/>
@@ -16096,7 +16096,7 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>A3--301</t>
+          <t>A3-301</t>
         </is>
       </c>
       <c r="B288" s="1" t="inlineStr"/>
@@ -16204,7 +16204,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>A3--401</t>
+          <t>A3-401</t>
         </is>
       </c>
       <c r="B290" s="1" t="inlineStr"/>
@@ -16420,7 +16420,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>A3--701</t>
+          <t>A3-701</t>
         </is>
       </c>
       <c r="B294" s="1" t="inlineStr"/>
@@ -16528,7 +16528,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>A3--801</t>
+          <t>A3-801</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr">
@@ -16802,7 +16802,7 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>A4--000</t>
+          <t>A4-000</t>
         </is>
       </c>
       <c r="B301" s="1" t="inlineStr"/>
@@ -16914,7 +16914,7 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>A4--111</t>
+          <t>A4-111</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr"/>
@@ -17022,7 +17022,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>A4--121</t>
+          <t>A4-121</t>
         </is>
       </c>
       <c r="B305" s="1" t="inlineStr"/>
@@ -17238,7 +17238,7 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>A4--131</t>
+          <t>A4-131</t>
         </is>
       </c>
       <c r="B309" s="1" t="inlineStr"/>
@@ -17400,7 +17400,7 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>A4--141</t>
+          <t>A4-141</t>
         </is>
       </c>
       <c r="B312" s="1" t="inlineStr"/>
@@ -17616,7 +17616,7 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>A4---202</t>
+          <t>A4-202</t>
         </is>
       </c>
       <c r="B316" s="1" t="inlineStr"/>
@@ -17778,7 +17778,7 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>A4--301</t>
+          <t>A4-301</t>
         </is>
       </c>
       <c r="B319" s="1" t="inlineStr"/>
@@ -17886,7 +17886,7 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>A4--401</t>
+          <t>A4-401</t>
         </is>
       </c>
       <c r="B321" s="1" t="inlineStr"/>
@@ -17994,7 +17994,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>A4--501</t>
+          <t>A4-501</t>
         </is>
       </c>
       <c r="B323" s="1" t="inlineStr"/>
@@ -18318,7 +18318,7 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>A4--701</t>
+          <t>A4-701</t>
         </is>
       </c>
       <c r="B329" s="1" t="inlineStr"/>
@@ -18534,7 +18534,7 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>A5--000</t>
+          <t>A5-000</t>
         </is>
       </c>
       <c r="B333" s="1" t="inlineStr"/>
@@ -18700,7 +18700,7 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>A5--121</t>
+          <t>A5-121</t>
         </is>
       </c>
       <c r="B336" s="1" t="inlineStr"/>
@@ -18808,7 +18808,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>A5--131</t>
+          <t>A5-131</t>
         </is>
       </c>
       <c r="B338" s="1" t="inlineStr"/>
@@ -18970,7 +18970,7 @@
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>A5--201</t>
+          <t>A5-201</t>
         </is>
       </c>
       <c r="B341" s="1" t="inlineStr"/>
@@ -19078,7 +19078,7 @@
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>A5--301</t>
+          <t>A5-301</t>
         </is>
       </c>
       <c r="B343" s="1" t="inlineStr"/>
@@ -19294,7 +19294,7 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>A5--601</t>
+          <t>A5-601</t>
         </is>
       </c>
       <c r="B347" s="1" t="inlineStr"/>
@@ -19402,7 +19402,7 @@
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>A6--000</t>
+          <t>A6-000</t>
         </is>
       </c>
       <c r="B349" s="1" t="inlineStr"/>
@@ -19510,7 +19510,7 @@
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>A6--111</t>
+          <t>A6-111</t>
         </is>
       </c>
       <c r="B351" s="1" t="inlineStr"/>
@@ -19672,7 +19672,7 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>A6--301</t>
+          <t>A6-301</t>
         </is>
       </c>
       <c r="B354" s="1" t="inlineStr"/>
@@ -19888,7 +19888,7 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>A7--101</t>
+          <t>A7-101</t>
         </is>
       </c>
       <c r="B358" s="1" t="inlineStr"/>
